--- a/project/stage03/analysis.xlsx
+++ b/project/stage03/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jantar\uni-data-warehouse\project\stage03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C56ADF1-F630-4BEA-AB40-F38E3150B910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B34051-7248-439E-BC57-6979ECC90A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="5" activeTab="9" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="1" activeTab="5" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
   </bookViews>
   <sheets>
     <sheet name="RainVsPitStops" sheetId="1" r:id="rId1"/>
@@ -26,20 +26,20 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="398" r:id="rId11"/>
-    <pivotCache cacheId="401" r:id="rId12"/>
-    <pivotCache cacheId="404" r:id="rId13"/>
-    <pivotCache cacheId="407" r:id="rId14"/>
-    <pivotCache cacheId="410" r:id="rId15"/>
-    <pivotCache cacheId="413" r:id="rId16"/>
-    <pivotCache cacheId="416" r:id="rId17"/>
-    <pivotCache cacheId="419" r:id="rId18"/>
-    <pivotCache cacheId="422" r:id="rId19"/>
-    <pivotCache cacheId="425" r:id="rId20"/>
-    <pivotCache cacheId="428" r:id="rId21"/>
-    <pivotCache cacheId="431" r:id="rId22"/>
-    <pivotCache cacheId="434" r:id="rId23"/>
-    <pivotCache cacheId="440" r:id="rId24"/>
+    <pivotCache cacheId="0" r:id="rId11"/>
+    <pivotCache cacheId="1" r:id="rId12"/>
+    <pivotCache cacheId="2" r:id="rId13"/>
+    <pivotCache cacheId="3" r:id="rId14"/>
+    <pivotCache cacheId="4" r:id="rId15"/>
+    <pivotCache cacheId="5" r:id="rId16"/>
+    <pivotCache cacheId="6" r:id="rId17"/>
+    <pivotCache cacheId="7" r:id="rId18"/>
+    <pivotCache cacheId="8" r:id="rId19"/>
+    <pivotCache cacheId="9" r:id="rId20"/>
+    <pivotCache cacheId="10" r:id="rId21"/>
+    <pivotCache cacheId="11" r:id="rId22"/>
+    <pivotCache cacheId="12" r:id="rId23"/>
+    <pivotCache cacheId="13" r:id="rId24"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -1344,7 +1344,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1358,7 +1358,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -2514,7 +2513,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2713,6 +2712,20 @@
           <a:effectLst/>
         </c:spPr>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -2746,6 +2759,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A57B-4A24-9AEC-ECB739D7B8A7}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -4204,7 +4222,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -4213,6 +4231,9 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -4269,6 +4290,9 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
               <a:schemeClr val="accent1"/>
@@ -17477,6 +17501,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="536128527"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -18291,6 +18316,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="532057039"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -18469,7 +18495,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="pl-PL"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -18522,7 +18548,6 @@
               <a:endParaRPr lang="pl-PL"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -18533,6 +18558,146 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -18567,6 +18732,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -18582,6 +18752,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -18597,6 +18772,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -18612,6 +18792,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -18627,6 +18812,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
@@ -18642,6 +18832,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
@@ -18659,6 +18854,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
@@ -18676,6 +18876,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
@@ -18693,6 +18898,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
@@ -18710,6 +18920,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-CCF9-42E0-A89B-3C53AED1CB29}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:cat>
             <c:strRef>
@@ -18795,7 +19010,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -25685,13 +25899,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>142875</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>128586</xdr:rowOff>
+      <xdr:rowOff>128585</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>733425</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>133349</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>437030</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>134470</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -28425,7 +28639,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="428" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:D12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -28682,7 +28896,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="407" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A1:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -28854,225 +29068,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="401" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="3">
-    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
-    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
-    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="78">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="11" level="1">
-        <member name="[Dim Time].[Year].&amp;[2010]"/>
-        <member name="[Dim Time].[Year].&amp;[2011]"/>
-        <member name="[Dim Time].[Year].&amp;[2012]"/>
-        <member name="[Dim Time].[Year].&amp;[2013]"/>
-        <member name="[Dim Time].[Year].&amp;[2014]"/>
-        <member name="[Dim Time].[Year].&amp;[2015]"/>
-        <member name="[Dim Time].[Year].&amp;[2016]"/>
-        <member name="[Dim Time].[Year].&amp;[2017]"/>
-        <member name="[Dim Time].[Year].&amp;[2018]"/>
-        <member name="[Dim Time].[Year].&amp;[2019]"/>
-        <member name="[Dim Time].[Year].&amp;[2020]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" id="1" iMeasureHier="53">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="26"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="404" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29153,7 +29149,7 @@
   <dataFields count="1">
     <dataField fld="2" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="10">
+  <chartFormats count="11">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -29271,6 +29267,18 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="0" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotHierarchies count="78">
     <pivotHierarchy/>
@@ -29335,6 +29343,344 @@
         <member name="[Dim Time].[Year].&amp;[1958]"/>
         <member name="[Dim Time].[Year].&amp;[1959]"/>
         <member name="[Dim Time].[Year].&amp;[1960]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="53">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="26"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
+    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
+    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="11">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="78">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="11" level="1">
+        <member name="[Dim Time].[Year].&amp;[2010]"/>
+        <member name="[Dim Time].[Year].&amp;[2011]"/>
+        <member name="[Dim Time].[Year].&amp;[2012]"/>
+        <member name="[Dim Time].[Year].&amp;[2013]"/>
+        <member name="[Dim Time].[Year].&amp;[2014]"/>
+        <member name="[Dim Time].[Year].&amp;[2015]"/>
+        <member name="[Dim Time].[Year].&amp;[2016]"/>
+        <member name="[Dim Time].[Year].&amp;[2017]"/>
+        <member name="[Dim Time].[Year].&amp;[2018]"/>
+        <member name="[Dim Time].[Year].&amp;[2019]"/>
+        <member name="[Dim Time].[Year].&amp;[2020]"/>
       </members>
     </pivotHierarchy>
     <pivotHierarchy/>
@@ -29403,7 +29749,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="398" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
   <location ref="A1:G7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29653,7 +29999,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="440" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A3:B78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -30087,7 +30433,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="431" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
   <location ref="A4:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -30641,7 +30987,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48529DB8-E948-488C-A714-CF42C15C483B}" name="PivotTable2" cacheId="419" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48529DB8-E948-488C-A714-CF42C15C483B}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="F34:G58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -30894,7 +31240,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="416" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
   <location ref="A3:G5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -31148,7 +31494,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="425" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
   <location ref="K5:U14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="5">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -31500,7 +31846,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="422" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -31761,7 +32107,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="413" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32069,7 +32415,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="410" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A1:C29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32323,7 +32669,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="434" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A12:C18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32872,13 +33218,13 @@
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>1.4611872146118721</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>1.3251533742331287</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6">
         <v>1.4031413612565444</v>
       </c>
     </row>
@@ -32886,13 +33232,13 @@
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>1.4928774928774928</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>2.1724137931034484</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>1.5892420537897312</v>
       </c>
     </row>
@@ -32900,13 +33246,13 @@
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>1.904040404040404</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8">
         <v>1.9661016949152543</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8">
         <v>1.9182879377431907</v>
       </c>
     </row>
@@ -32914,13 +33260,13 @@
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>1.9824561403508771</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9">
         <v>2.36</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9">
         <v>2.0611111111111109</v>
       </c>
     </row>
@@ -32928,13 +33274,13 @@
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>1.9039735099337749</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10">
         <v>2.1296296296296298</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10">
         <v>1.9634146341463414</v>
       </c>
     </row>
@@ -32942,13 +33288,13 @@
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>1.8850931677018634</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11">
         <v>3.2105263157894739</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11">
         <v>2.1870503597122304</v>
       </c>
     </row>
@@ -32956,13 +33302,13 @@
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>1.7698270721526534</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12">
         <v>2.096774193548387</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12">
         <v>1.8514541387024608</v>
       </c>
     </row>
@@ -33002,7 +33348,7 @@
       <c r="A4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="7">
         <v>10335466.666666666</v>
       </c>
     </row>
@@ -33010,7 +33356,7 @@
       <c r="A5" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="7">
         <v>9771600</v>
       </c>
     </row>
@@ -33018,7 +33364,7 @@
       <c r="A6" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="7">
         <v>10324950</v>
       </c>
     </row>
@@ -33026,7 +33372,7 @@
       <c r="A7" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="7">
         <v>10186600</v>
       </c>
     </row>
@@ -33034,7 +33380,7 @@
       <c r="A8" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="7">
         <v>10067900</v>
       </c>
     </row>
@@ -33042,7 +33388,7 @@
       <c r="A9" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9" s="7">
         <v>8775500</v>
       </c>
     </row>
@@ -33050,7 +33396,7 @@
       <c r="A10" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10" s="7">
         <v>8625100</v>
       </c>
     </row>
@@ -33058,7 +33404,7 @@
       <c r="A11" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11" s="7">
         <v>9324500</v>
       </c>
     </row>
@@ -33066,7 +33412,7 @@
       <c r="A12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12" s="7">
         <v>7445300</v>
       </c>
     </row>
@@ -33074,7 +33420,7 @@
       <c r="A13" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13" s="7">
         <v>7495100</v>
       </c>
     </row>
@@ -33082,7 +33428,7 @@
       <c r="A14" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="7">
         <v>8543000</v>
       </c>
     </row>
@@ -33090,7 +33436,7 @@
       <c r="A15" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15" s="7">
         <v>7493100</v>
       </c>
     </row>
@@ -33098,7 +33444,7 @@
       <c r="A16" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16" s="7">
         <v>8995820</v>
       </c>
     </row>
@@ -33106,7 +33452,7 @@
       <c r="A17" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17" s="7">
         <v>8707100</v>
       </c>
     </row>
@@ -33114,7 +33460,7 @@
       <c r="A18" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18" s="7">
         <v>7884800</v>
       </c>
     </row>
@@ -33122,7 +33468,7 @@
       <c r="A19" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19" s="7">
         <v>7516725</v>
       </c>
     </row>
@@ -33130,7 +33476,7 @@
       <c r="A20" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20" s="7">
         <v>6438766.666666667</v>
       </c>
     </row>
@@ -33138,7 +33484,7 @@
       <c r="A21" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21" s="7">
         <v>6244975</v>
       </c>
     </row>
@@ -33146,7 +33492,7 @@
       <c r="A22" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22" s="7">
         <v>6073800</v>
       </c>
     </row>
@@ -33154,7 +33500,7 @@
       <c r="A23" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23" s="7">
         <v>5958036</v>
       </c>
     </row>
@@ -33162,7 +33508,7 @@
       <c r="A24" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24" s="7">
         <v>5961691.666666667</v>
       </c>
     </row>
@@ -33170,7 +33516,7 @@
       <c r="A25" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25" s="7">
         <v>4709468.5714285718</v>
       </c>
     </row>
@@ -33178,7 +33524,7 @@
       <c r="A26" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26" s="7">
         <v>5435316.666666667</v>
       </c>
     </row>
@@ -33186,7 +33532,7 @@
       <c r="A27" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27" s="7">
         <v>5393785.7142857146</v>
       </c>
     </row>
@@ -33194,7 +33540,7 @@
       <c r="A28" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28" s="7">
         <v>5004900</v>
       </c>
     </row>
@@ -33202,7 +33548,7 @@
       <c r="A29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29" s="7">
         <v>5000583.333333333</v>
       </c>
     </row>
@@ -33210,7 +33556,7 @@
       <c r="A30" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30" s="7">
         <v>5472763.6363636367</v>
       </c>
     </row>
@@ -33218,7 +33564,7 @@
       <c r="A31" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31" s="7">
         <v>5300033.333333333</v>
       </c>
     </row>
@@ -33226,7 +33572,7 @@
       <c r="A32" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32" s="7">
         <v>4066579.0909090908</v>
       </c>
     </row>
@@ -33234,7 +33580,7 @@
       <c r="A33" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="B33" s="8">
+      <c r="B33" s="7">
         <v>4958081.4285714282</v>
       </c>
     </row>
@@ -33242,7 +33588,7 @@
       <c r="A34" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B34" s="8">
+      <c r="B34" s="7">
         <v>5248934.2</v>
       </c>
     </row>
@@ -33250,7 +33596,7 @@
       <c r="A35" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B35" s="8">
+      <c r="B35" s="7">
         <v>4983324.25</v>
       </c>
     </row>
@@ -33258,7 +33604,7 @@
       <c r="A36" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="8">
+      <c r="B36" s="7">
         <v>5037734</v>
       </c>
     </row>
@@ -33266,7 +33612,7 @@
       <c r="A37" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="B37" s="8">
+      <c r="B37" s="7">
         <v>4841189.5</v>
       </c>
     </row>
@@ -33274,7 +33620,7 @@
       <c r="A38" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="B38" s="8">
+      <c r="B38" s="7">
         <v>4722609.5</v>
       </c>
     </row>
@@ -33282,7 +33628,7 @@
       <c r="A39" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="B39" s="8">
+      <c r="B39" s="7">
         <v>4684527</v>
       </c>
     </row>
@@ -33290,7 +33636,7 @@
       <c r="A40" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="B40" s="8">
+      <c r="B40" s="7">
         <v>4534194.833333333</v>
       </c>
     </row>
@@ -33298,7 +33644,7 @@
       <c r="A41" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B41" s="8">
+      <c r="B41" s="7">
         <v>4703726.125</v>
       </c>
     </row>
@@ -33306,7 +33652,7 @@
       <c r="A42" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="B42" s="8">
+      <c r="B42" s="7">
         <v>4782805.75</v>
       </c>
     </row>
@@ -33314,7 +33660,7 @@
       <c r="A43" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="B43" s="8">
+      <c r="B43" s="7">
         <v>4708868.2</v>
       </c>
     </row>
@@ -33322,7 +33668,7 @@
       <c r="A44" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B44" s="8">
+      <c r="B44" s="7">
         <v>4707697.5</v>
       </c>
     </row>
@@ -33330,7 +33676,7 @@
       <c r="A45" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B45" s="8">
+      <c r="B45" s="7">
         <v>4739363.2</v>
       </c>
     </row>
@@ -33338,7 +33684,7 @@
       <c r="A46" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B46" s="8">
+      <c r="B46" s="7">
         <v>4647515</v>
       </c>
     </row>
@@ -33346,7 +33692,7 @@
       <c r="A47" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="B47" s="8">
+      <c r="B47" s="7">
         <v>4716555.8</v>
       </c>
     </row>
@@ -33354,7 +33700,7 @@
       <c r="A48" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B48" s="8">
+      <c r="B48" s="7">
         <v>4725496.75</v>
       </c>
     </row>
@@ -33362,7 +33708,7 @@
       <c r="A49" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="B49" s="8">
+      <c r="B49" s="7">
         <v>4714750.4000000004</v>
       </c>
     </row>
@@ -33370,7 +33716,7 @@
       <c r="A50" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B50" s="8">
+      <c r="B50" s="7">
         <v>4646023.9090909092</v>
       </c>
     </row>
@@ -33378,7 +33724,7 @@
       <c r="A51" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="B51" s="8">
+      <c r="B51" s="7">
         <v>4674193.333333333</v>
       </c>
     </row>
@@ -33386,7 +33732,7 @@
       <c r="A52" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B52" s="8">
+      <c r="B52" s="7">
         <v>4647590.9000000004</v>
       </c>
     </row>
@@ -33394,7 +33740,7 @@
       <c r="A53" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="B53" s="8">
+      <c r="B53" s="7">
         <v>5293787.833333333</v>
       </c>
     </row>
@@ -33402,7 +33748,7 @@
       <c r="A54" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B54" s="8">
+      <c r="B54" s="7">
         <v>4659644.5714285718</v>
       </c>
     </row>
@@ -33410,7 +33756,7 @@
       <c r="A55" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="B55" s="8">
+      <c r="B55" s="7">
         <v>4635018.5999999996</v>
       </c>
     </row>
@@ -33418,7 +33764,7 @@
       <c r="A56" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="B56" s="8">
+      <c r="B56" s="7">
         <v>4471408.8</v>
       </c>
     </row>
@@ -33426,7 +33772,7 @@
       <c r="A57" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="B57" s="8">
+      <c r="B57" s="7">
         <v>4551856.7272727275</v>
       </c>
     </row>
@@ -33434,7 +33780,7 @@
       <c r="A58" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B58" s="8">
+      <c r="B58" s="7">
         <v>4508729.0999999996</v>
       </c>
     </row>
@@ -33442,7 +33788,7 @@
       <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="B59" s="8">
+      <c r="B59" s="7">
         <v>4526991.7</v>
       </c>
     </row>
@@ -33450,7 +33796,7 @@
       <c r="A60" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="B60" s="8">
+      <c r="B60" s="7">
         <v>4767425</v>
       </c>
     </row>
@@ -33458,7 +33804,7 @@
       <c r="A61" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B61" s="8">
+      <c r="B61" s="7">
         <v>5247373</v>
       </c>
     </row>
@@ -33466,7 +33812,7 @@
       <c r="A62" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B62" s="8">
+      <c r="B62" s="7">
         <v>4651278.6363636367</v>
       </c>
     </row>
@@ -33474,7 +33820,7 @@
       <c r="A63" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="B63" s="8">
+      <c r="B63" s="7">
         <v>4621699.461538462</v>
       </c>
     </row>
@@ -33482,7 +33828,7 @@
       <c r="A64" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="B64" s="8">
+      <c r="B64" s="7">
         <v>4866103</v>
       </c>
     </row>
@@ -33490,7 +33836,7 @@
       <c r="A65" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B65" s="8">
+      <c r="B65" s="7">
         <v>4816472.153846154</v>
       </c>
     </row>
@@ -33498,7 +33844,7 @@
       <c r="A66" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="B66" s="8">
+      <c r="B66" s="7">
         <v>4740358.4666666668</v>
       </c>
     </row>
@@ -33506,7 +33852,7 @@
       <c r="A67" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B67" s="8">
+      <c r="B67" s="7">
         <v>4800346.076923077</v>
       </c>
     </row>
@@ -33514,7 +33860,7 @@
       <c r="A68" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B68" s="8">
+      <c r="B68" s="7">
         <v>4724407.333333333</v>
       </c>
     </row>
@@ -33522,7 +33868,7 @@
       <c r="A69" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="B69" s="8">
+      <c r="B69" s="7">
         <v>4690428.4000000004</v>
       </c>
     </row>
@@ -33530,7 +33876,7 @@
       <c r="A70" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="B70" s="8">
+      <c r="B70" s="7">
         <v>4580867.444444444</v>
       </c>
     </row>
@@ -33538,7 +33884,7 @@
       <c r="A71" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B71" s="8">
+      <c r="B71" s="7">
         <v>4648709.444444444</v>
       </c>
     </row>
@@ -33546,7 +33892,7 @@
       <c r="A72" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B72" s="8">
+      <c r="B72" s="7">
         <v>4570080.375</v>
       </c>
     </row>
@@ -33554,7 +33900,7 @@
       <c r="A73" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B73" s="8">
+      <c r="B73" s="7">
         <v>6447325.8125</v>
       </c>
     </row>
@@ -33562,7 +33908,7 @@
       <c r="A74" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B74" s="8">
+      <c r="B74" s="7">
         <v>4931917.4666666668</v>
       </c>
     </row>
@@ -33570,7 +33916,7 @@
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B75" s="8">
+      <c r="B75" s="7">
         <v>4833085.166666667</v>
       </c>
     </row>
@@ -33578,7 +33924,7 @@
       <c r="A76" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B76" s="8">
+      <c r="B76" s="7">
         <v>4469108.9375</v>
       </c>
     </row>
@@ -33586,7 +33932,7 @@
       <c r="A77" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B77" s="8">
+      <c r="B77" s="7">
         <v>4523655.153846154</v>
       </c>
     </row>
@@ -33594,7 +33940,7 @@
       <c r="A78" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B78" s="8">
+      <c r="B78" s="7">
         <v>5245271.0078431377</v>
       </c>
     </row>
@@ -33658,19 +34004,17 @@
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="7"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>1.2086570477247502</v>
       </c>
     </row>
@@ -33678,13 +34022,12 @@
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="7"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>0.56140350877192979</v>
       </c>
     </row>
@@ -33692,7 +34035,7 @@
       <c r="A10" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>3.4645390070921986</v>
       </c>
     </row>
@@ -33700,7 +34043,7 @@
       <c r="A11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>1.4308426073131955</v>
       </c>
     </row>
@@ -33708,13 +34051,12 @@
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="7"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>1.1666666666666667</v>
       </c>
     </row>
@@ -33722,7 +34064,7 @@
       <c r="A14" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>4.2163742690058479</v>
       </c>
     </row>
@@ -33730,7 +34072,7 @@
       <c r="A15" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>2.6777546777546779</v>
       </c>
     </row>
@@ -33738,7 +34080,7 @@
       <c r="A16" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>1.1880952380952381</v>
       </c>
     </row>
@@ -33746,7 +34088,7 @@
       <c r="A17" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17">
         <v>1.0948616600790513</v>
       </c>
     </row>
@@ -33754,7 +34096,7 @@
       <c r="A18" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18">
         <v>0.94680851063829785</v>
       </c>
     </row>
@@ -33762,13 +34104,12 @@
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="7"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20">
         <v>2.3026737967914439</v>
       </c>
     </row>
@@ -33776,7 +34117,7 @@
       <c r="A21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21">
         <v>0.98565573770491799</v>
       </c>
     </row>
@@ -33784,7 +34125,7 @@
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22">
         <v>1.6894683372841179</v>
       </c>
     </row>
@@ -33852,22 +34193,22 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>4.5844155844155843</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>5.6934426229508199</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>9.9909836065573767</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>12.158196721311475</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>12.445081967213115</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5">
         <v>9.7461449498843482</v>
       </c>
     </row>
@@ -33911,7 +34252,7 @@
       <c r="F35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="7">
+      <c r="G35">
         <v>12.445081967213115</v>
       </c>
       <c r="J35" s="2" t="s">
@@ -33925,7 +34266,7 @@
       <c r="F36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G36" s="7">
+      <c r="G36">
         <v>12.158196721311475</v>
       </c>
       <c r="J36" s="2" t="s">
@@ -33939,7 +34280,7 @@
       <c r="F37" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="7">
+      <c r="G37">
         <v>9.9909836065573767</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -33953,7 +34294,7 @@
       <c r="F38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G38" s="7">
+      <c r="G38">
         <v>5.6934426229508199</v>
       </c>
     </row>
@@ -33961,7 +34302,7 @@
       <c r="F39" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="7">
+      <c r="G39">
         <v>4.5844155844155843</v>
       </c>
     </row>
@@ -33969,7 +34310,7 @@
       <c r="F40" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40">
         <v>3.7236842105263159</v>
       </c>
     </row>
@@ -33977,7 +34318,7 @@
       <c r="F41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41">
         <v>3.0649717514124295</v>
       </c>
     </row>
@@ -33985,7 +34326,7 @@
       <c r="F42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42">
         <v>2.7666666666666666</v>
       </c>
     </row>
@@ -33993,7 +34334,7 @@
       <c r="F43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43">
         <v>2.7333333333333334</v>
       </c>
     </row>
@@ -34001,7 +34342,7 @@
       <c r="F44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44">
         <v>2.5181159420289854</v>
       </c>
     </row>
@@ -34009,7 +34350,7 @@
       <c r="F45" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45">
         <v>1.8433734939759037</v>
       </c>
     </row>
@@ -34017,7 +34358,7 @@
       <c r="F46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46">
         <v>1.6995073891625616</v>
       </c>
     </row>
@@ -34025,7 +34366,7 @@
       <c r="F47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47">
         <v>1.1212121212121211</v>
       </c>
     </row>
@@ -34033,7 +34374,7 @@
       <c r="F48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48">
         <v>0.91044776119402981</v>
       </c>
     </row>
@@ -34041,7 +34382,7 @@
       <c r="F49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49">
         <v>0.83333333333333337</v>
       </c>
     </row>
@@ -34049,7 +34390,7 @@
       <c r="F50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50">
         <v>0.77105263157894732</v>
       </c>
     </row>
@@ -34057,7 +34398,7 @@
       <c r="F51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51">
         <v>0.70673076923076927</v>
       </c>
     </row>
@@ -34065,7 +34406,7 @@
       <c r="F52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52">
         <v>1.834862385321101E-2</v>
       </c>
     </row>
@@ -34073,7 +34414,7 @@
       <c r="F53" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53">
         <v>1.282051282051282E-2</v>
       </c>
     </row>
@@ -34081,7 +34422,7 @@
       <c r="F54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54">
         <v>0</v>
       </c>
     </row>
@@ -34089,7 +34430,7 @@
       <c r="F55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55">
         <v>0</v>
       </c>
     </row>
@@ -34097,7 +34438,7 @@
       <c r="F56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56">
         <v>0</v>
       </c>
     </row>
@@ -34105,7 +34446,7 @@
       <c r="F57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57">
         <v>0</v>
       </c>
     </row>
@@ -34113,7 +34454,7 @@
       <c r="F58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58">
         <v>4.8117619639527653</v>
       </c>
     </row>
@@ -34795,7 +35136,7 @@
       <c r="A6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>7.333333333333333</v>
       </c>
     </row>
@@ -34803,7 +35144,7 @@
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>10.857142857142858</v>
       </c>
     </row>
@@ -34811,7 +35152,7 @@
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>12.461538461538462</v>
       </c>
     </row>
@@ -34819,7 +35160,7 @@
       <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>9.2666666666666675</v>
       </c>
     </row>
@@ -34827,7 +35168,7 @@
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>6.7058823529411766</v>
       </c>
     </row>
@@ -34835,7 +35176,7 @@
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>10</v>
       </c>
     </row>
@@ -34843,7 +35184,7 @@
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>22.181818181818183</v>
       </c>
     </row>
@@ -34851,7 +35192,7 @@
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>15.846153846153847</v>
       </c>
     </row>
@@ -34859,7 +35200,7 @@
       <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>15.571428571428571</v>
       </c>
     </row>
@@ -34867,7 +35208,7 @@
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>17.642857142857142</v>
       </c>
     </row>
@@ -34875,7 +35216,7 @@
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>20.23076923076923</v>
       </c>
     </row>
@@ -34883,7 +35224,7 @@
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17">
         <v>15.642857142857142</v>
       </c>
     </row>
@@ -34891,7 +35232,7 @@
       <c r="A18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18">
         <v>16.866666666666667</v>
       </c>
     </row>
@@ -34899,7 +35240,7 @@
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19">
         <v>19.23076923076923</v>
       </c>
     </row>
@@ -34907,7 +35248,7 @@
       <c r="A20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20">
         <v>21.23076923076923</v>
       </c>
     </row>
@@ -34915,7 +35256,7 @@
       <c r="A21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21">
         <v>37.75</v>
       </c>
     </row>
@@ -34923,7 +35264,7 @@
       <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22">
         <v>32.222222222222221</v>
       </c>
     </row>
@@ -34931,7 +35272,7 @@
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23">
         <v>25.833333333333332</v>
       </c>
     </row>
@@ -34939,7 +35280,7 @@
       <c r="A24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24">
         <v>42.375</v>
       </c>
     </row>
@@ -34947,7 +35288,7 @@
       <c r="A25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25">
         <v>24.166666666666668</v>
       </c>
     </row>
@@ -34955,7 +35296,7 @@
       <c r="A26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26">
         <v>20.636363636363637</v>
       </c>
     </row>
@@ -34963,7 +35304,7 @@
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27">
         <v>28.857142857142858</v>
       </c>
     </row>
@@ -34971,7 +35312,7 @@
       <c r="A28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28">
         <v>31</v>
       </c>
     </row>
@@ -34979,7 +35320,7 @@
       <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29">
         <v>30.333333333333332</v>
       </c>
     </row>
@@ -34987,7 +35328,7 @@
       <c r="A30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30">
         <v>41.5</v>
       </c>
     </row>
@@ -34995,7 +35336,7 @@
       <c r="A31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31">
         <v>36</v>
       </c>
     </row>
@@ -35003,7 +35344,7 @@
       <c r="A32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32">
         <v>18.508710801393729</v>
       </c>
     </row>
@@ -35039,15 +35380,11 @@
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -35075,8 +35412,6 @@
       <c r="A6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -35115,8 +35450,6 @@
       <c r="A10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -35155,8 +35488,6 @@
       <c r="A14" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -35184,15 +35515,11 @@
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -35220,8 +35547,6 @@
       <c r="A21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -35249,8 +35574,6 @@
       <c r="A24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
@@ -35278,8 +35601,6 @@
       <c r="A27" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -35338,7 +35659,7 @@
       <c r="B2" s="5">
         <v>0.44833759590792838</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2">
         <v>22.692165044042653</v>
       </c>
     </row>
@@ -35349,7 +35670,7 @@
       <c r="B3" s="5">
         <v>0.43169697798441131</v>
       </c>
-      <c r="C3" s="7">
+      <c r="C3">
         <v>21.970163618864294</v>
       </c>
     </row>
@@ -35360,7 +35681,7 @@
       <c r="B4" s="5">
         <v>0.43795322234705342</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>23.093403598037433</v>
       </c>
     </row>
@@ -35371,7 +35692,7 @@
       <c r="B5" s="5">
         <v>0.36974938228026827</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>20.745169420330441</v>
       </c>
     </row>
@@ -35382,7 +35703,7 @@
       <c r="B6" s="5">
         <v>0.28947368421052633</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>16.462962962962962</v>
       </c>
     </row>
@@ -35393,7 +35714,7 @@
       <c r="B7" s="5">
         <v>0.42289579907310509</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>22.168771452626125</v>
       </c>
     </row>
@@ -35415,7 +35736,7 @@
       <c r="B13" s="5">
         <v>7.1859063514140009E-2</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>204.97563624511076</v>
       </c>
     </row>
@@ -35426,7 +35747,7 @@
       <c r="B14" s="5">
         <v>9.3840230991337828E-2</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="7">
         <v>205.16611265899439</v>
       </c>
     </row>
@@ -35437,7 +35758,7 @@
       <c r="B15" s="5">
         <v>7.8502634926403775E-2</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>203.2058367206337</v>
       </c>
     </row>
@@ -35448,7 +35769,7 @@
       <c r="B16" s="5">
         <v>4.2005040604872583E-2</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>204.29969566736577</v>
       </c>
     </row>
@@ -35459,7 +35780,7 @@
       <c r="B17" s="5">
         <v>1.8518518518518517E-2</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>200.14666666666656</v>
       </c>
     </row>
@@ -35470,7 +35791,7 @@
       <c r="B18" s="5">
         <v>7.3052263454439478E-2</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="7">
         <v>204.11633034415902</v>
       </c>
     </row>
@@ -35551,13 +35872,13 @@
       <c r="A6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>232</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6">
         <v>70</v>
       </c>
     </row>
@@ -35565,13 +35886,13 @@
       <c r="A7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7">
         <v>47</v>
       </c>
     </row>
@@ -35579,13 +35900,13 @@
       <c r="A8" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8">
         <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8">
         <v>37</v>
       </c>
     </row>
@@ -35593,13 +35914,13 @@
       <c r="A9" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9">
         <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9">
         <v>35</v>
       </c>
     </row>
@@ -35607,13 +35928,13 @@
       <c r="A10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10">
         <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="7">
+      <c r="G10">
         <v>30</v>
       </c>
     </row>
@@ -35621,13 +35942,13 @@
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11">
         <v>26</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G11" s="7">
+      <c r="G11">
         <v>25</v>
       </c>
     </row>
@@ -35635,13 +35956,13 @@
       <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12">
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G12" s="7">
+      <c r="G12">
         <v>17</v>
       </c>
     </row>
@@ -35649,13 +35970,13 @@
       <c r="A13" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13">
         <v>17</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="7">
+      <c r="G13">
         <v>15</v>
       </c>
     </row>
@@ -35663,13 +35984,13 @@
       <c r="A14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14">
         <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14">
         <v>12</v>
       </c>
     </row>
@@ -35677,13 +35998,13 @@
       <c r="A15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15">
         <v>15</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G15" s="7">
+      <c r="G15">
         <v>9</v>
       </c>
     </row>
@@ -35691,13 +36012,13 @@
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16">
         <v>524</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G16">
         <v>297</v>
       </c>
     </row>
@@ -35763,22 +36084,22 @@
       <c r="A4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4">
         <v>5</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4">
         <v>121</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4">
         <v>2</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4">
         <v>46</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4">
         <v>7</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4">
         <v>167</v>
       </c>
     </row>
@@ -35786,22 +36107,22 @@
       <c r="A5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5">
         <v>3</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5">
         <v>132</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5">
         <v>39</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5">
         <v>171</v>
       </c>
     </row>
@@ -35809,18 +36130,16 @@
       <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
@@ -35828,22 +36147,22 @@
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7">
         <v>258</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7">
         <v>8</v>
       </c>
-      <c r="E7" s="7">
+      <c r="E7">
         <v>85</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7">
         <v>17</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7">
         <v>343</v>
       </c>
     </row>

--- a/project/stage03/analysis.xlsx
+++ b/project/stage03/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jantar\uni-data-warehouse\project\stage03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B34051-7248-439E-BC57-6979ECC90A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5540BB3B-B167-420C-9801-3F7FFF8E1AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="1" activeTab="5" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="4" activeTab="10" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
   </bookViews>
   <sheets>
     <sheet name="RainVsPitStops" sheetId="1" r:id="rId1"/>
@@ -23,23 +23,25 @@
     <sheet name="Top 10 reasons for Mechanical" sheetId="9" r:id="rId8"/>
     <sheet name="Podium from in or out weather" sheetId="10" r:id="rId9"/>
     <sheet name="Average Race Time in Autodromo " sheetId="11" r:id="rId10"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId11"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId11"/>
-    <pivotCache cacheId="1" r:id="rId12"/>
-    <pivotCache cacheId="2" r:id="rId13"/>
-    <pivotCache cacheId="3" r:id="rId14"/>
-    <pivotCache cacheId="4" r:id="rId15"/>
-    <pivotCache cacheId="5" r:id="rId16"/>
-    <pivotCache cacheId="6" r:id="rId17"/>
-    <pivotCache cacheId="7" r:id="rId18"/>
-    <pivotCache cacheId="8" r:id="rId19"/>
-    <pivotCache cacheId="9" r:id="rId20"/>
-    <pivotCache cacheId="10" r:id="rId21"/>
-    <pivotCache cacheId="11" r:id="rId22"/>
-    <pivotCache cacheId="12" r:id="rId23"/>
-    <pivotCache cacheId="13" r:id="rId24"/>
+    <pivotCache cacheId="132" r:id="rId12"/>
+    <pivotCache cacheId="135" r:id="rId13"/>
+    <pivotCache cacheId="138" r:id="rId14"/>
+    <pivotCache cacheId="141" r:id="rId15"/>
+    <pivotCache cacheId="144" r:id="rId16"/>
+    <pivotCache cacheId="147" r:id="rId17"/>
+    <pivotCache cacheId="150" r:id="rId18"/>
+    <pivotCache cacheId="153" r:id="rId19"/>
+    <pivotCache cacheId="156" r:id="rId20"/>
+    <pivotCache cacheId="159" r:id="rId21"/>
+    <pivotCache cacheId="162" r:id="rId22"/>
+    <pivotCache cacheId="165" r:id="rId23"/>
+    <pivotCache cacheId="168" r:id="rId24"/>
+    <pivotCache cacheId="171" r:id="rId25"/>
+    <pivotCache cacheId="174" r:id="rId26"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -153,7 +155,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="228">
   <si>
     <t>AveragePitStopsCount</t>
   </si>
@@ -826,6 +828,18 @@
   <si>
     <t>Average Race Time in Minutes</t>
   </si>
+  <si>
+    <t>Constructor Reliability KPI</t>
+  </si>
+  <si>
+    <t>Constructor Reliability KPI Goal</t>
+  </si>
+  <si>
+    <t>Constructor Reliability KPI Status</t>
+  </si>
+  <si>
+    <t>Constructor Reliability KPI Trend</t>
+  </si>
 </sst>
 </file>
 
@@ -1344,7 +1358,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1359,6 +1373,7 @@
       <alignment horizontal="left" indent="2"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1931,6 +1946,15 @@
             <c:idx val="3"/>
             <c:invertIfNegative val="0"/>
             <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                 <c16:uniqueId val="{00000000-F922-4D18-8E8C-10340D2E2DAB}"/>
@@ -26211,23 +26235,383 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620473842595" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7D06339B-CF30-4D37-AE3F-EEB11A431A55}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650479166667" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{EDAF3AB4-F84F-4D58-B645-530C9DA3FC38}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" numFmtId="0" hierarchy="78" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" numFmtId="0" hierarchy="79" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" numFmtId="0" hierarchy="80" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" numFmtId="0" hierarchy="81" level="32767"/>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="25">
+        <s v="[Dim Time].[Year].&amp;[2000]" c="2000"/>
+        <s v="[Dim Time].[Year].&amp;[2001]" c="2001"/>
+        <s v="[Dim Time].[Year].&amp;[2002]" c="2002"/>
+        <s v="[Dim Time].[Year].&amp;[2003]" c="2003"/>
+        <s v="[Dim Time].[Year].&amp;[2004]" c="2004"/>
+        <s v="[Dim Time].[Year].&amp;[2005]" c="2005"/>
+        <s v="[Dim Time].[Year].&amp;[2006]" c="2006"/>
+        <s v="[Dim Time].[Year].&amp;[2007]" c="2007"/>
+        <s v="[Dim Time].[Year].&amp;[2008]" c="2008"/>
+        <s v="[Dim Time].[Year].&amp;[2009]" c="2009"/>
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" iconSet="8" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" iconSet="5" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.65048715278" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3962C440-443E-4D75-B22B-0E43959F42B2}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="4">
+    <cacheField name="[Degenerate Details].[Grid Position].[Grid Position]" caption="Grid Position" numFmtId="0" hierarchy="4" level="1">
+      <sharedItems count="30">
+        <s v="[Degenerate Details].[Grid Position].&amp;[1]" c="1"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[2]" c="2"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[3]" c="3"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[4]" c="4"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[5]" c="5"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[6]" c="6"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[7]" c="7"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[8]" c="8"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[9]" c="9"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[10]" c="10"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[11]" c="11"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[12]" c="12"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[13]" c="13"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[14]" c="14"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[15]" c="15"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[16]" c="16"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[17]" c="17"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[18]" c="18"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[19]" c="19"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[20]" c="20"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[21]" c="21"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[22]" c="22"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[23]" c="23"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[24]" c="24"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[25]" c="25"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[26]" c="26"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[28]" u="1" c="28"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[29]" u="1" c="29"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[31]" u="1" c="31"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[32]" u="1" c="32"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
+    <cacheField name="[Dim Race].[Race Name Official].[Race Name Official]" caption="Race Name Official" numFmtId="0" hierarchy="22" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650487962965" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5251863D-400F-43FD-A0F1-A4BBAAFEDC07}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
     <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
-      <sharedItems count="3">
+      <sharedItems count="2">
         <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
         <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
-        <s v="[Dim Weather].[Did Rain Occur].[All].UNKNOWNMEMBER" u="1" c="Unknown"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Dim Weather].[Humidity Category].[Humidity Category]" caption="Humidity Category" numFmtId="0" hierarchy="40" level="1">
-      <sharedItems count="5">
-        <s v="[Dim Weather].[Humidity Category].&amp;[Comfortable]" c="Comfortable"/>
-        <s v="[Dim Weather].[Humidity Category].&amp;[Dry]" c="Dry"/>
-        <s v="[Dim Weather].[Humidity Category].&amp;[Humid]" c="Humid"/>
-        <s v="[Dim Weather].[Humidity Category].&amp;[Very Dry]" c="Very Dry"/>
-        <s v="[Dim Weather].[Humidity Category].&amp;[Very Humid]" c="Very Humid"/>
+    <cacheField name="[Dim Weather].[Track Temp Category].[Track Temp Category]" caption="Track Temp Category" numFmtId="0" hierarchy="42" level="1">
+      <sharedItems count="4">
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Cool Track]" c="Cool Track"/>
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Hot Track]" c="Hot Track"/>
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Optimal Track]" c="Optimal Track"/>
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Very Hot Track]" c="Very Hot Track"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Dim Weather].[Wind Speed Category].[Wind Speed Category]" caption="Wind Speed Category" numFmtId="0" hierarchy="44" level="1">
@@ -26237,10 +26621,10 @@
         <s v="[Dim Weather].[Wind Speed Category].&amp;[Moderate Breeze]" c="Moderate Breeze"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" numFmtId="0" hierarchy="61" level="32767"/>
-    <cacheField name="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" numFmtId="0" hierarchy="62" level="32767"/>
+    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
+    <cacheField name="[Measures].[Finish Percentage]" caption="Finish Percentage" numFmtId="0" hierarchy="74" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
@@ -26286,14 +26670,14 @@
         <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
@@ -26301,190 +26685,6 @@
         <fieldUsage x="2"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620481365739" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{70BBC5B2-939A-459F-88F4-8193C9E44ED3}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="6">
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Driver].[Full Name].[Full Name]" caption="Full Name" numFmtId="0" hierarchy="19" level="1">
-      <sharedItems count="9">
-        <s v="[Dim Driver].[Full Name].&amp;[Carlos Sainz]" c="Carlos Sainz"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Charles Leclerc]" c="Charles Leclerc"/>
-        <s v="[Dim Driver].[Full Name].&amp;[George Russell]" c="George Russell"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Kimi Räikkönen]" c="Kimi Räikkönen"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Lando Norris]" c="Lando Norris"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Lewis Hamilton]" c="Lewis Hamilton"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Max Verstappen]" c="Max Verstappen"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Sebastian Vettel]" c="Sebastian Vettel"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Valtteri Bottas]" c="Valtteri Bottas"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Driver].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="16" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
-    <cacheField name="[Dim Race].[Year Season].[Year Season]" caption="Year Season" numFmtId="0" hierarchy="24" level="1">
-      <sharedItems count="7">
-        <s v="[Dim Race].[Year Season].&amp;[2018]" c="2018"/>
-        <s v="[Dim Race].[Year Season].&amp;[2019]" c="2019"/>
-        <s v="[Dim Race].[Year Season].&amp;[2020]" c="2020"/>
-        <s v="[Dim Race].[Year Season].&amp;[2021]" c="2021"/>
-        <s v="[Dim Race].[Year Season].&amp;[2022]" c="2022"/>
-        <s v="[Dim Race].[Year Season].&amp;[2023]" c="2023"/>
-        <s v="[Dim Race].[Year Season].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
@@ -26513,187 +26713,27 @@
     <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="3"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.62048229167" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{19EFFABB-3DF1-4D82-9260-5ADF45140058}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="7">
-    <cacheField name="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" numFmtId="0" hierarchy="68" level="32767"/>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Year]" caption="Year" numFmtId="0" hierarchy="36" level="1">
-      <sharedItems count="6">
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2023]" c="2023"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="36" level="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Month]" caption="Month" numFmtId="0" hierarchy="36" level="3">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Day Of Month]" caption="Day Of Month" numFmtId="0" hierarchy="36" level="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
-      <sharedItems count="3">
-        <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
-        <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
-        <s v="[Dim Weather].[Did Rain Occur].[All].UNKNOWNMEMBER" u="1" c="Unknown"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="5" unbalanced="0">
-      <fieldsUsage count="5">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-        <fieldUsage x="2"/>
-        <fieldUsage x="3"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -26727,217 +26767,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620483217594" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{83FC3B7F-BBEF-4612-AC70-0D06FDFFB172}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="7">
-    <cacheField name="[Dim Circuit].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="7" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" numFmtId="0" hierarchy="69" level="32767"/>
-    <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
-      <sharedItems count="30">
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Charade Circuit]" c="Charade Circuit"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Nevers Magny-Cours]" c="Circuit de Nevers Magny-Cours"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Spa-Francorchamps]" c="Circuit de Spa-Francorchamps"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Paul Ricard]" c="Circuit Paul Ricard"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Dijon-Prenois]" c="Dijon-Prenois"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Hockenheimring]" c="Hockenheimring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Nivelles-Baulers]" c="Nivelles-Baulers"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Nürburgring]" c="Nürburgring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Red Bull Ring]" c="Red Bull Ring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Reims-Gueux]" c="Reims-Gueux"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Rouen-Les-Essarts]" c="Rouen-Les-Essarts"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Zolder]" c="Zolder"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Aintree]" u="1" c="Aintree"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Enzo e Dino Ferrari]" u="1" c="Autodromo Enzo e Dino Ferrari"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Nazionale di Monza]" u="1" c="Autodromo Nazionale di Monza"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Autódromo do Estoril]" u="1" c="Autódromo do Estoril"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Brands Hatch]" u="1" c="Brands Hatch"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Bremgarten]" u="1" c="Circuit Bremgarten"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Barcelona-Catalunya]" u="1" c="Circuit de Barcelona-Catalunya"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Monaco]" u="1" c="Circuit de Monaco"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Pedralbes]" u="1" c="Circuit de Pedralbes"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Park Zandvoort]" u="1" c="Circuit Park Zandvoort"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuito de Jerez]" u="1" c="Circuito de Jerez"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Donington Park]" u="1" c="Donington Park"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Hungaroring]" u="1" c="Hungaroring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Jarama]" u="1" c="Jarama"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Scandinavian Raceway]" u="1" c="Scandinavian Raceway"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Silverstone Circuit]" u="1" c="Silverstone Circuit"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Sochi Autodrom]" u="1" c="Sochi Autodrom"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Valencia Street Circuit]" u="1" c="Valencia Street Circuit"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Continent]" caption="Continent" numFmtId="0" hierarchy="10" level="1">
-      <sharedItems count="1">
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe]" c="Europe"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Country Name]" caption="Country Name" numFmtId="0" hierarchy="10" level="2">
-      <sharedItems count="4">
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria]" c="Austria"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium]" c="Belgium"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France]" c="France"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany]" c="Germany"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Location City]" caption="Location City" numFmtId="0" hierarchy="10" level="3">
-      <sharedItems count="12">
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria].&amp;[Spielberg]" c="Spielberg"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Brussels]" c="Brussels"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Heusden-Zolder]" c="Heusden-Zolder"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Spa]" c="Spa"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Clermont-Ferrand]" c="Clermont-Ferrand"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Dijon]" c="Dijon"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Le Castellet]" c="Le Castellet"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Magny Cours]" c="Magny Cours"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Reims]" c="Reims"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Rouen]" c="Rouen"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Hockenheim]" c="Hockenheim"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Nürburg]" c="Nürburg"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="10" level="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="5" unbalanced="0">
-      <fieldsUsage count="5">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-        <fieldUsage x="4"/>
-        <fieldUsage x="5"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.62048391204" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1BD78FDA-7D69-4F13-9DC2-8B3D9C96FD22}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650488657404" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{91EA7F40-35C5-4637-AD47-C1EF62F40064}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Degenerate Details].[Age Group].[Age Group]" caption="Age Group" numFmtId="0" hierarchy="1" level="1">
@@ -26949,10 +26779,10 @@
         <s v="[Degenerate Details].[Age Group].&amp;[Under 20]" c="Under 20"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
-    <cacheField name="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" numFmtId="0" hierarchy="76" level="32767"/>
+    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
+    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
@@ -27030,22 +26860,28 @@
     <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -27078,388 +26914,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.6205619213" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{125F41B5-3B3C-4D18-ADBF-159F41F79641}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="74">
-        <s v="[Dim Time].[Year].&amp;[1950]" c="1950"/>
-        <s v="[Dim Time].[Year].&amp;[1951]" c="1951"/>
-        <s v="[Dim Time].[Year].&amp;[1952]" c="1952"/>
-        <s v="[Dim Time].[Year].&amp;[1953]" c="1953"/>
-        <s v="[Dim Time].[Year].&amp;[1954]" c="1954"/>
-        <s v="[Dim Time].[Year].&amp;[1955]" c="1955"/>
-        <s v="[Dim Time].[Year].&amp;[1956]" c="1956"/>
-        <s v="[Dim Time].[Year].&amp;[1957]" c="1957"/>
-        <s v="[Dim Time].[Year].&amp;[1958]" c="1958"/>
-        <s v="[Dim Time].[Year].&amp;[1959]" c="1959"/>
-        <s v="[Dim Time].[Year].&amp;[1960]" c="1960"/>
-        <s v="[Dim Time].[Year].&amp;[1961]" c="1961"/>
-        <s v="[Dim Time].[Year].&amp;[1962]" c="1962"/>
-        <s v="[Dim Time].[Year].&amp;[1963]" c="1963"/>
-        <s v="[Dim Time].[Year].&amp;[1964]" c="1964"/>
-        <s v="[Dim Time].[Year].&amp;[1965]" c="1965"/>
-        <s v="[Dim Time].[Year].&amp;[1966]" c="1966"/>
-        <s v="[Dim Time].[Year].&amp;[1967]" c="1967"/>
-        <s v="[Dim Time].[Year].&amp;[1968]" c="1968"/>
-        <s v="[Dim Time].[Year].&amp;[1969]" c="1969"/>
-        <s v="[Dim Time].[Year].&amp;[1970]" c="1970"/>
-        <s v="[Dim Time].[Year].&amp;[1971]" c="1971"/>
-        <s v="[Dim Time].[Year].&amp;[1972]" c="1972"/>
-        <s v="[Dim Time].[Year].&amp;[1973]" c="1973"/>
-        <s v="[Dim Time].[Year].&amp;[1974]" c="1974"/>
-        <s v="[Dim Time].[Year].&amp;[1975]" c="1975"/>
-        <s v="[Dim Time].[Year].&amp;[1976]" c="1976"/>
-        <s v="[Dim Time].[Year].&amp;[1977]" c="1977"/>
-        <s v="[Dim Time].[Year].&amp;[1978]" c="1978"/>
-        <s v="[Dim Time].[Year].&amp;[1979]" c="1979"/>
-        <s v="[Dim Time].[Year].&amp;[1981]" c="1981"/>
-        <s v="[Dim Time].[Year].&amp;[1982]" c="1982"/>
-        <s v="[Dim Time].[Year].&amp;[1983]" c="1983"/>
-        <s v="[Dim Time].[Year].&amp;[1984]" c="1984"/>
-        <s v="[Dim Time].[Year].&amp;[1985]" c="1985"/>
-        <s v="[Dim Time].[Year].&amp;[1986]" c="1986"/>
-        <s v="[Dim Time].[Year].&amp;[1987]" c="1987"/>
-        <s v="[Dim Time].[Year].&amp;[1988]" c="1988"/>
-        <s v="[Dim Time].[Year].&amp;[1989]" c="1989"/>
-        <s v="[Dim Time].[Year].&amp;[1990]" c="1990"/>
-        <s v="[Dim Time].[Year].&amp;[1991]" c="1991"/>
-        <s v="[Dim Time].[Year].&amp;[1992]" c="1992"/>
-        <s v="[Dim Time].[Year].&amp;[1993]" c="1993"/>
-        <s v="[Dim Time].[Year].&amp;[1994]" c="1994"/>
-        <s v="[Dim Time].[Year].&amp;[1995]" c="1995"/>
-        <s v="[Dim Time].[Year].&amp;[1996]" c="1996"/>
-        <s v="[Dim Time].[Year].&amp;[1997]" c="1997"/>
-        <s v="[Dim Time].[Year].&amp;[1998]" c="1998"/>
-        <s v="[Dim Time].[Year].&amp;[1999]" c="1999"/>
-        <s v="[Dim Time].[Year].&amp;[2000]" c="2000"/>
-        <s v="[Dim Time].[Year].&amp;[2001]" c="2001"/>
-        <s v="[Dim Time].[Year].&amp;[2002]" c="2002"/>
-        <s v="[Dim Time].[Year].&amp;[2003]" c="2003"/>
-        <s v="[Dim Time].[Year].&amp;[2004]" c="2004"/>
-        <s v="[Dim Time].[Year].&amp;[2005]" c="2005"/>
-        <s v="[Dim Time].[Year].&amp;[2006]" c="2006"/>
-        <s v="[Dim Time].[Year].&amp;[2007]" c="2007"/>
-        <s v="[Dim Time].[Year].&amp;[2008]" c="2008"/>
-        <s v="[Dim Time].[Year].&amp;[2009]" c="2009"/>
-        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
-        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
-        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
-        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
-        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
-        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
-        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
-        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" numFmtId="0" hierarchy="77" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.62047465278" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{8FE8892F-6B13-44C4-9323-FDA7B9542767}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
-      <sharedItems count="10">
-        <s v="[Dim Status].[Status Description].&amp;[Brakes]" c="Brakes"/>
-        <s v="[Dim Status].[Status Description].&amp;[Electrical]" c="Electrical"/>
-        <s v="[Dim Status].[Status Description].&amp;[Engine]" c="Engine"/>
-        <s v="[Dim Status].[Status Description].&amp;[Gearbox]" c="Gearbox"/>
-        <s v="[Dim Status].[Status Description].&amp;[Hydraulics]" c="Hydraulics"/>
-        <s v="[Dim Status].[Status Description].&amp;[Mechanical]" c="Mechanical"/>
-        <s v="[Dim Status].[Status Description].&amp;[Power Unit]" c="Power Unit"/>
-        <s v="[Dim Status].[Status Description].&amp;[Puncture]" c="Puncture"/>
-        <s v="[Dim Status].[Status Description].&amp;[Suspension]" c="Suspension"/>
-        <s v="[Dim Status].[Status Description].&amp;[Wheel]" c="Wheel"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Status].[Status Category].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="25" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Constructor].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620475578704" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{22B37FF6-6A8A-4281-AC48-8C27DD0DC8A1}">
+<file path=xl/pivotCache/pivotCacheDefinition13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650489583335" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{22B37FF6-6A8A-4281-AC48-8C27DD0DC8A1}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="6">
     <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
@@ -27490,7 +26946,7 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
@@ -27598,8 +27054,14 @@
     <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -27632,8 +27094,572 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.62047627315" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{91EA7F40-35C5-4637-AD47-C1EF62F40064}">
+<file path=xl/pivotCache/pivotCacheDefinition14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650490509259" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{8FE8892F-6B13-44C4-9323-FDA7B9542767}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
+      <sharedItems count="10">
+        <s v="[Dim Status].[Status Description].&amp;[Brakes]" c="Brakes"/>
+        <s v="[Dim Status].[Status Description].&amp;[Electrical]" c="Electrical"/>
+        <s v="[Dim Status].[Status Description].&amp;[Engine]" c="Engine"/>
+        <s v="[Dim Status].[Status Description].&amp;[Gearbox]" c="Gearbox"/>
+        <s v="[Dim Status].[Status Description].&amp;[Hydraulics]" c="Hydraulics"/>
+        <s v="[Dim Status].[Status Description].&amp;[Mechanical]" c="Mechanical"/>
+        <s v="[Dim Status].[Status Description].&amp;[Power Unit]" c="Power Unit"/>
+        <s v="[Dim Status].[Status Description].&amp;[Puncture]" c="Puncture"/>
+        <s v="[Dim Status].[Status Description].&amp;[Suspension]" c="Suspension"/>
+        <s v="[Dim Status].[Status Description].&amp;[Wheel]" c="Wheel"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Status].[Status Category].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="25" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Constructor].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650491319444" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7D06339B-CF30-4D37-AE3F-EEB11A431A55}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
+      <sharedItems count="3">
+        <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
+        <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
+        <s v="[Dim Weather].[Did Rain Occur].[All].UNKNOWNMEMBER" u="1" c="Unknown"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Weather].[Humidity Category].[Humidity Category]" caption="Humidity Category" numFmtId="0" hierarchy="40" level="1">
+      <sharedItems count="5">
+        <s v="[Dim Weather].[Humidity Category].&amp;[Comfortable]" c="Comfortable"/>
+        <s v="[Dim Weather].[Humidity Category].&amp;[Dry]" c="Dry"/>
+        <s v="[Dim Weather].[Humidity Category].&amp;[Humid]" c="Humid"/>
+        <s v="[Dim Weather].[Humidity Category].&amp;[Very Dry]" c="Very Dry"/>
+        <s v="[Dim Weather].[Humidity Category].&amp;[Very Humid]" c="Very Humid"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Weather].[Wind Speed Category].[Wind Speed Category]" caption="Wind Speed Category" numFmtId="0" hierarchy="44" level="1">
+      <sharedItems count="3">
+        <s v="[Dim Weather].[Wind Speed Category].&amp;[Calm]" c="Calm"/>
+        <s v="[Dim Weather].[Wind Speed Category].&amp;[Light Breeze]" c="Light Breeze"/>
+        <s v="[Dim Weather].[Wind Speed Category].&amp;[Moderate Breeze]" c="Moderate Breeze"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" numFmtId="0" hierarchy="61" level="32767"/>
+    <cacheField name="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" numFmtId="0" hierarchy="62" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650480324075" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{125F41B5-3B3C-4D18-ADBF-159F41F79641}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="74">
+        <s v="[Dim Time].[Year].&amp;[1950]" c="1950"/>
+        <s v="[Dim Time].[Year].&amp;[1951]" c="1951"/>
+        <s v="[Dim Time].[Year].&amp;[1952]" c="1952"/>
+        <s v="[Dim Time].[Year].&amp;[1953]" c="1953"/>
+        <s v="[Dim Time].[Year].&amp;[1954]" c="1954"/>
+        <s v="[Dim Time].[Year].&amp;[1955]" c="1955"/>
+        <s v="[Dim Time].[Year].&amp;[1956]" c="1956"/>
+        <s v="[Dim Time].[Year].&amp;[1957]" c="1957"/>
+        <s v="[Dim Time].[Year].&amp;[1958]" c="1958"/>
+        <s v="[Dim Time].[Year].&amp;[1959]" c="1959"/>
+        <s v="[Dim Time].[Year].&amp;[1960]" c="1960"/>
+        <s v="[Dim Time].[Year].&amp;[1961]" c="1961"/>
+        <s v="[Dim Time].[Year].&amp;[1962]" c="1962"/>
+        <s v="[Dim Time].[Year].&amp;[1963]" c="1963"/>
+        <s v="[Dim Time].[Year].&amp;[1964]" c="1964"/>
+        <s v="[Dim Time].[Year].&amp;[1965]" c="1965"/>
+        <s v="[Dim Time].[Year].&amp;[1966]" c="1966"/>
+        <s v="[Dim Time].[Year].&amp;[1967]" c="1967"/>
+        <s v="[Dim Time].[Year].&amp;[1968]" c="1968"/>
+        <s v="[Dim Time].[Year].&amp;[1969]" c="1969"/>
+        <s v="[Dim Time].[Year].&amp;[1970]" c="1970"/>
+        <s v="[Dim Time].[Year].&amp;[1971]" c="1971"/>
+        <s v="[Dim Time].[Year].&amp;[1972]" c="1972"/>
+        <s v="[Dim Time].[Year].&amp;[1973]" c="1973"/>
+        <s v="[Dim Time].[Year].&amp;[1974]" c="1974"/>
+        <s v="[Dim Time].[Year].&amp;[1975]" c="1975"/>
+        <s v="[Dim Time].[Year].&amp;[1976]" c="1976"/>
+        <s v="[Dim Time].[Year].&amp;[1977]" c="1977"/>
+        <s v="[Dim Time].[Year].&amp;[1978]" c="1978"/>
+        <s v="[Dim Time].[Year].&amp;[1979]" c="1979"/>
+        <s v="[Dim Time].[Year].&amp;[1981]" c="1981"/>
+        <s v="[Dim Time].[Year].&amp;[1982]" c="1982"/>
+        <s v="[Dim Time].[Year].&amp;[1983]" c="1983"/>
+        <s v="[Dim Time].[Year].&amp;[1984]" c="1984"/>
+        <s v="[Dim Time].[Year].&amp;[1985]" c="1985"/>
+        <s v="[Dim Time].[Year].&amp;[1986]" c="1986"/>
+        <s v="[Dim Time].[Year].&amp;[1987]" c="1987"/>
+        <s v="[Dim Time].[Year].&amp;[1988]" c="1988"/>
+        <s v="[Dim Time].[Year].&amp;[1989]" c="1989"/>
+        <s v="[Dim Time].[Year].&amp;[1990]" c="1990"/>
+        <s v="[Dim Time].[Year].&amp;[1991]" c="1991"/>
+        <s v="[Dim Time].[Year].&amp;[1992]" c="1992"/>
+        <s v="[Dim Time].[Year].&amp;[1993]" c="1993"/>
+        <s v="[Dim Time].[Year].&amp;[1994]" c="1994"/>
+        <s v="[Dim Time].[Year].&amp;[1995]" c="1995"/>
+        <s v="[Dim Time].[Year].&amp;[1996]" c="1996"/>
+        <s v="[Dim Time].[Year].&amp;[1997]" c="1997"/>
+        <s v="[Dim Time].[Year].&amp;[1998]" c="1998"/>
+        <s v="[Dim Time].[Year].&amp;[1999]" c="1999"/>
+        <s v="[Dim Time].[Year].&amp;[2000]" c="2000"/>
+        <s v="[Dim Time].[Year].&amp;[2001]" c="2001"/>
+        <s v="[Dim Time].[Year].&amp;[2002]" c="2002"/>
+        <s v="[Dim Time].[Year].&amp;[2003]" c="2003"/>
+        <s v="[Dim Time].[Year].&amp;[2004]" c="2004"/>
+        <s v="[Dim Time].[Year].&amp;[2005]" c="2005"/>
+        <s v="[Dim Time].[Year].&amp;[2006]" c="2006"/>
+        <s v="[Dim Time].[Year].&amp;[2007]" c="2007"/>
+        <s v="[Dim Time].[Year].&amp;[2008]" c="2008"/>
+        <s v="[Dim Time].[Year].&amp;[2009]" c="2009"/>
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" numFmtId="0" hierarchy="77" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650480902776" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1BD78FDA-7D69-4F13-9DC2-8B3D9C96FD22}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Degenerate Details].[Age Group].[Age Group]" caption="Age Group" numFmtId="0" hierarchy="1" level="1">
@@ -27645,10 +27671,10 @@
         <s v="[Degenerate Details].[Age Group].&amp;[Under 20]" c="Under 20"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
-    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
+    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
+    <cacheField name="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" numFmtId="0" hierarchy="76" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
@@ -27726,22 +27752,244 @@
     <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="2"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650481944445" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{83FC3B7F-BBEF-4612-AC70-0D06FDFFB172}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="7">
+    <cacheField name="[Dim Circuit].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="7" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" numFmtId="0" hierarchy="69" level="32767"/>
+    <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
+      <sharedItems count="30">
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Charade Circuit]" c="Charade Circuit"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Nevers Magny-Cours]" c="Circuit de Nevers Magny-Cours"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Spa-Francorchamps]" c="Circuit de Spa-Francorchamps"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Paul Ricard]" c="Circuit Paul Ricard"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Dijon-Prenois]" c="Dijon-Prenois"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Hockenheimring]" c="Hockenheimring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Nivelles-Baulers]" c="Nivelles-Baulers"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Nürburgring]" c="Nürburgring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Red Bull Ring]" c="Red Bull Ring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Reims-Gueux]" c="Reims-Gueux"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Rouen-Les-Essarts]" c="Rouen-Les-Essarts"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Zolder]" c="Zolder"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Aintree]" u="1" c="Aintree"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Enzo e Dino Ferrari]" u="1" c="Autodromo Enzo e Dino Ferrari"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Nazionale di Monza]" u="1" c="Autodromo Nazionale di Monza"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Autódromo do Estoril]" u="1" c="Autódromo do Estoril"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Brands Hatch]" u="1" c="Brands Hatch"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Bremgarten]" u="1" c="Circuit Bremgarten"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Barcelona-Catalunya]" u="1" c="Circuit de Barcelona-Catalunya"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Monaco]" u="1" c="Circuit de Monaco"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Pedralbes]" u="1" c="Circuit de Pedralbes"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Park Zandvoort]" u="1" c="Circuit Park Zandvoort"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuito de Jerez]" u="1" c="Circuito de Jerez"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Donington Park]" u="1" c="Donington Park"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Hungaroring]" u="1" c="Hungaroring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Jarama]" u="1" c="Jarama"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Scandinavian Raceway]" u="1" c="Scandinavian Raceway"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Silverstone Circuit]" u="1" c="Silverstone Circuit"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Sochi Autodrom]" u="1" c="Sochi Autodrom"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Valencia Street Circuit]" u="1" c="Valencia Street Circuit"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Continent]" caption="Continent" numFmtId="0" hierarchy="10" level="1">
+      <sharedItems count="1">
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe]" c="Europe"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Country Name]" caption="Country Name" numFmtId="0" hierarchy="10" level="2">
+      <sharedItems count="4">
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria]" c="Austria"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium]" c="Belgium"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France]" c="France"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany]" c="Germany"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Location City]" caption="Location City" numFmtId="0" hierarchy="10" level="3">
+      <sharedItems count="12">
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria].&amp;[Spielberg]" c="Spielberg"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Brussels]" c="Brussels"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Heusden-Zolder]" c="Heusden-Zolder"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Spa]" c="Spa"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Clermont-Ferrand]" c="Clermont-Ferrand"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Dijon]" c="Dijon"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Le Castellet]" c="Le Castellet"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Magny Cours]" c="Magny Cours"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Reims]" c="Reims"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Rouen]" c="Rouen"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Hockenheim]" c="Hockenheim"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Nürburg]" c="Nürburg"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="10" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+        <fieldUsage x="4"/>
+        <fieldUsage x="5"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -27775,34 +28023,41 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620477083336" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5251863D-400F-43FD-A0F1-A4BBAAFEDC07}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650482870369" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{19EFFABB-3DF1-4D82-9260-5ADF45140058}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
+  <cacheFields count="7">
+    <cacheField name="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" numFmtId="0" hierarchy="68" level="32767"/>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Year]" caption="Year" numFmtId="0" hierarchy="36" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2023]" c="2023"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="36" level="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Month]" caption="Month" numFmtId="0" hierarchy="36" level="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Day Of Month]" caption="Day Of Month" numFmtId="0" hierarchy="36" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
     <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
-      <sharedItems count="2">
+      <sharedItems count="3">
         <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
         <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
+        <s v="[Dim Weather].[Did Rain Occur].[All].UNKNOWNMEMBER" u="1" c="Unknown"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Dim Weather].[Track Temp Category].[Track Temp Category]" caption="Track Temp Category" numFmtId="0" hierarchy="42" level="1">
-      <sharedItems count="4">
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Cool Track]" c="Cool Track"/>
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Hot Track]" c="Hot Track"/>
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Optimal Track]" c="Optimal Track"/>
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Very Hot Track]" c="Very Hot Track"/>
-      </sharedItems>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
-    <cacheField name="[Dim Weather].[Wind Speed Category].[Wind Speed Category]" caption="Wind Speed Category" numFmtId="0" hierarchy="44" level="1">
-      <sharedItems count="3">
-        <s v="[Dim Weather].[Wind Speed Category].&amp;[Calm]" c="Calm"/>
-        <s v="[Dim Weather].[Wind Speed Category].&amp;[Light Breeze]" c="Light Breeze"/>
-        <s v="[Dim Weather].[Wind Speed Category].&amp;[Moderate Breeze]" c="Moderate Breeze"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
-    <cacheField name="[Measures].[Finish Percentage]" caption="Finish Percentage" numFmtId="0" hierarchy="74" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
@@ -27839,30 +28094,33 @@
     <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+        <fieldUsage x="2"/>
+        <fieldUsage x="3"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
+        <fieldUsage x="5"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
@@ -27886,26 +28144,28 @@
     <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -27939,62 +28199,54 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620478009259" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3962C440-443E-4D75-B22B-0E43959F42B2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650483680554" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{70BBC5B2-939A-459F-88F4-8193C9E44ED3}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="4">
-    <cacheField name="[Degenerate Details].[Grid Position].[Grid Position]" caption="Grid Position" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems count="30">
-        <s v="[Degenerate Details].[Grid Position].&amp;[1]" c="1"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[2]" c="2"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[3]" c="3"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[4]" c="4"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[5]" c="5"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[6]" c="6"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[7]" c="7"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[8]" c="8"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[9]" c="9"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[10]" c="10"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[11]" c="11"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[12]" c="12"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[13]" c="13"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[14]" c="14"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[15]" c="15"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[16]" c="16"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[17]" c="17"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[18]" c="18"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[19]" c="19"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[20]" c="20"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[21]" c="21"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[22]" c="22"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[23]" c="23"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[24]" c="24"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[25]" c="25"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[26]" c="26"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[28]" u="1" c="28"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[29]" u="1" c="29"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[31]" u="1" c="31"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[32]" u="1" c="32"/>
+  <cacheFields count="5">
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
-    <cacheField name="[Dim Race].[Race Name Official].[Race Name Official]" caption="Race Name Official" numFmtId="0" hierarchy="22" level="1">
+    <cacheField name="[Dim Driver].[Full Name].[Full Name]" caption="Full Name" numFmtId="0" hierarchy="19" level="1">
+      <sharedItems count="9">
+        <s v="[Dim Driver].[Full Name].&amp;[Carlos Sainz]" c="Carlos Sainz"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Charles Leclerc]" c="Charles Leclerc"/>
+        <s v="[Dim Driver].[Full Name].&amp;[George Russell]" c="George Russell"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Kimi Räikkönen]" c="Kimi Räikkönen"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Lando Norris]" c="Lando Norris"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Lewis Hamilton]" c="Lewis Hamilton"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Max Verstappen]" c="Max Verstappen"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Sebastian Vettel]" c="Sebastian Vettel"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Valtteri Bottas]" c="Valtteri Bottas"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Driver].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="16" level="1">
       <sharedItems containsSemiMixedTypes="0" containsString="0"/>
     </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
+    <cacheField name="[Dim Race].[Year Season].[Year Season]" caption="Year Season" numFmtId="0" hierarchy="24" level="1">
+      <sharedItems count="7">
+        <s v="[Dim Race].[Year Season].&amp;[2018]" c="2018"/>
+        <s v="[Dim Race].[Year Season].&amp;[2019]" c="2019"/>
+        <s v="[Dim Race].[Year Season].&amp;[2020]" c="2020"/>
+        <s v="[Dim Race].[Year Season].&amp;[2021]" c="2021"/>
+        <s v="[Dim Race].[Year Season].&amp;[2022]" c="2022"/>
+        <s v="[Dim Race].[Year Season].&amp;[2023]" c="2023"/>
+        <s v="[Dim Race].[Year Season].&amp;[2024]" c="2024"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
@@ -28006,20 +28258,30 @@
     <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
         <fieldUsage x="2"/>
       </fieldsUsage>
     </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
@@ -28035,7 +28297,7 @@
     <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
+        <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
@@ -28072,18 +28334,24 @@
     <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
-        <fieldUsage x="1"/>
+        <fieldUsage x="3"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -28117,348 +28385,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620478935183" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{28154DEC-1536-40EA-A99D-9B5AD219ACD3}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
-    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems count="6">
-        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
-        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
-        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
-        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
-        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
-        <s v="[Dim Constructor].[Name].&amp;[Brawn]" u="1" c="Brawn"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="15">
-        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
-        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
-        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
-        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
-        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
-        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
-        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
-        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.62047962963" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C10063E3-D4E7-473D-BD5C-4113D4AFFA08}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
-    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems count="23">
-        <s v="[Dim Constructor].[Name].&amp;[Alfa Romeo]" c="Alfa Romeo"/>
-        <s v="[Dim Constructor].[Name].&amp;[AlphaTauri]" c="AlphaTauri"/>
-        <s v="[Dim Constructor].[Name].&amp;[Alpine F1 Team]" c="Alpine F1 Team"/>
-        <s v="[Dim Constructor].[Name].&amp;[Aston Martin]" c="Aston Martin"/>
-        <s v="[Dim Constructor].[Name].&amp;[Caterham]" c="Caterham"/>
-        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
-        <s v="[Dim Constructor].[Name].&amp;[Force India]" c="Force India"/>
-        <s v="[Dim Constructor].[Name].&amp;[Haas F1 Team]" c="Haas F1 Team"/>
-        <s v="[Dim Constructor].[Name].&amp;[HRT]" c="HRT"/>
-        <s v="[Dim Constructor].[Name].&amp;[Lotus]" c="Lotus"/>
-        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
-        <s v="[Dim Constructor].[Name].&amp;[Manor Marussia]" c="Manor Marussia"/>
-        <s v="[Dim Constructor].[Name].&amp;[Marussia]" c="Marussia"/>
-        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
-        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
-        <s v="[Dim Constructor].[Name].&amp;[Racing Point]" c="Racing Point"/>
-        <s v="[Dim Constructor].[Name].&amp;[RB F1 Team]" c="RB F1 Team"/>
-        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
-        <s v="[Dim Constructor].[Name].&amp;[Renault]" c="Renault"/>
-        <s v="[Dim Constructor].[Name].&amp;[Sauber]" c="Sauber"/>
-        <s v="[Dim Constructor].[Name].&amp;[Toro Rosso]" c="Toro Rosso"/>
-        <s v="[Dim Constructor].[Name].&amp;[Virgin]" c="Virgin"/>
-        <s v="[Dim Constructor].[Name].&amp;[Williams]" c="Williams"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="15">
-        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
-        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
-        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
-        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
-        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
-        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
-        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
-        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="78">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.620480555554" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{6819B2E0-02BE-4505-B7D4-5934BA61994A}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650484606478" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{6819B2E0-02BE-4505-B7D4-5934BA61994A}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="4">
     <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
@@ -28506,7 +28433,7 @@
     </cacheField>
     <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
   </cacheFields>
-  <cacheHierarchies count="78">
+  <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
@@ -28604,8 +28531,367 @@
     <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
-  <kpis count="0"/>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650485416663" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C10063E3-D4E7-473D-BD5C-4113D4AFFA08}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
+    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems count="23">
+        <s v="[Dim Constructor].[Name].&amp;[Alfa Romeo]" c="Alfa Romeo"/>
+        <s v="[Dim Constructor].[Name].&amp;[AlphaTauri]" c="AlphaTauri"/>
+        <s v="[Dim Constructor].[Name].&amp;[Alpine F1 Team]" c="Alpine F1 Team"/>
+        <s v="[Dim Constructor].[Name].&amp;[Aston Martin]" c="Aston Martin"/>
+        <s v="[Dim Constructor].[Name].&amp;[Caterham]" c="Caterham"/>
+        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
+        <s v="[Dim Constructor].[Name].&amp;[Force India]" c="Force India"/>
+        <s v="[Dim Constructor].[Name].&amp;[Haas F1 Team]" c="Haas F1 Team"/>
+        <s v="[Dim Constructor].[Name].&amp;[HRT]" c="HRT"/>
+        <s v="[Dim Constructor].[Name].&amp;[Lotus]" c="Lotus"/>
+        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
+        <s v="[Dim Constructor].[Name].&amp;[Manor Marussia]" c="Manor Marussia"/>
+        <s v="[Dim Constructor].[Name].&amp;[Marussia]" c="Marussia"/>
+        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
+        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
+        <s v="[Dim Constructor].[Name].&amp;[Racing Point]" c="Racing Point"/>
+        <s v="[Dim Constructor].[Name].&amp;[RB F1 Team]" c="RB F1 Team"/>
+        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
+        <s v="[Dim Constructor].[Name].&amp;[Renault]" c="Renault"/>
+        <s v="[Dim Constructor].[Name].&amp;[Sauber]" c="Sauber"/>
+        <s v="[Dim Constructor].[Name].&amp;[Toro Rosso]" c="Toro Rosso"/>
+        <s v="[Dim Constructor].[Name].&amp;[Virgin]" c="Virgin"/>
+        <s v="[Dim Constructor].[Name].&amp;[Williams]" c="Williams"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="15">
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.65048611111" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{28154DEC-1536-40EA-A99D-9B5AD219ACD3}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
+    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
+        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
+        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
+        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
+        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
+        <s v="[Dim Constructor].[Name].&amp;[Brawn]" u="1" c="Brawn"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="15">
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
   <dimensions count="9">
     <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
     <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
@@ -28639,7 +28925,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="144" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:D12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -28788,7 +29074,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -28876,6 +29162,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -28896,7 +29187,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="165" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A1:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -28969,85 +29260,90 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -29068,7 +29364,350 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="171" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
+    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
+    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="11">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="11" level="1">
+        <member name="[Dim Time].[Year].&amp;[2010]"/>
+        <member name="[Dim Time].[Year].&amp;[2011]"/>
+        <member name="[Dim Time].[Year].&amp;[2012]"/>
+        <member name="[Dim Time].[Year].&amp;[2013]"/>
+        <member name="[Dim Time].[Year].&amp;[2014]"/>
+        <member name="[Dim Time].[Year].&amp;[2015]"/>
+        <member name="[Dim Time].[Year].&amp;[2016]"/>
+        <member name="[Dim Time].[Year].&amp;[2017]"/>
+        <member name="[Dim Time].[Year].&amp;[2018]"/>
+        <member name="[Dim Time].[Year].&amp;[2019]"/>
+        <member name="[Dim Time].[Year].&amp;[2020]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="53">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="26"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="168" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29280,7 +29919,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -29385,344 +30024,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" id="1" iMeasureHier="53">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="26"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="3">
-    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
-    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
-    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="11">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="78">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="11" level="1">
-        <member name="[Dim Time].[Year].&amp;[2010]"/>
-        <member name="[Dim Time].[Year].&amp;[2011]"/>
-        <member name="[Dim Time].[Year].&amp;[2012]"/>
-        <member name="[Dim Time].[Year].&amp;[2013]"/>
-        <member name="[Dim Time].[Year].&amp;[2014]"/>
-        <member name="[Dim Time].[Year].&amp;[2015]"/>
-        <member name="[Dim Time].[Year].&amp;[2016]"/>
-        <member name="[Dim Time].[Year].&amp;[2017]"/>
-        <member name="[Dim Time].[Year].&amp;[2018]"/>
-        <member name="[Dim Time].[Year].&amp;[2019]"/>
-        <member name="[Dim Time].[Year].&amp;[2020]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <filters count="1">
@@ -29749,7 +30055,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="174" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
   <location ref="A1:G7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29899,85 +30205,90 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -29999,7 +30310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A3:B78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -30333,7 +30644,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -30416,6 +30727,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -30432,8 +30748,279 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB381D15-99CD-4BB2-BFAA-5B743EDB0261}" name="PivotTable1" cacheId="132" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A3:E29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="25">
+        <item s="1" x="0"/>
+        <item s="1" x="1"/>
+        <item s="1" x="2"/>
+        <item s="1" x="3"/>
+        <item s="1" x="4"/>
+        <item s="1" x="5"/>
+        <item s="1" x="6"/>
+        <item s="1" x="7"/>
+        <item s="1" x="8"/>
+        <item s="1" x="9"/>
+        <item s="1" x="10"/>
+        <item s="1" x="11"/>
+        <item s="1" x="12"/>
+        <item s="1" x="13"/>
+        <item s="1" x="14"/>
+        <item s="1" x="15"/>
+        <item s="1" x="16"/>
+        <item s="1" x="17"/>
+        <item s="1" x="18"/>
+        <item s="1" x="19"/>
+        <item s="1" x="20"/>
+        <item s="1" x="21"/>
+        <item s="1" x="22"/>
+        <item s="1" x="23"/>
+        <item s="1" x="24"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="26">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <dataFields count="4">
+    <dataField name="Constructor Reliability KPI" fld="0" baseField="0" baseItem="0"/>
+    <dataField name="Constructor Reliability KPI Goal" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Constructor Reliability KPI Status" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Constructor Reliability KPI Trend" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <conditionalFormats count="2">
+    <conditionalFormat scope="data" priority="2">
+      <pivotAreas count="1">
+        <pivotArea outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat scope="data" priority="1">
+      <pivotAreas count="1">
+        <pivotArea outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="37"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="141" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
   <location ref="A4:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -30791,7 +31378,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -30970,6 +31557,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -30987,7 +31579,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48529DB8-E948-488C-A714-CF42C15C483B}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48529DB8-E948-488C-A714-CF42C15C483B}" name="PivotTable2" cacheId="153" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="F34:G58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -31144,7 +31736,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -31223,6 +31815,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -31240,7 +31837,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="156" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
   <location ref="A3:G5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -31398,7 +31995,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -31477,6 +32074,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <colHierarchiesUsage count="1">
@@ -31494,7 +32096,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="147" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
   <location ref="K5:U14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="5">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -31733,7 +32335,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -31826,6 +32428,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -31846,7 +32453,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="150" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -31997,7 +32604,7 @@
   <dataFields count="1">
     <dataField fld="3" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -32090,6 +32697,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -32107,7 +32719,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32255,7 +32867,7 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
+  <pivotHierarchies count="83">
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -32398,6 +33010,11 @@
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
     <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -32415,7 +33032,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="162" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A1:C29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32568,85 +33185,90 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="3">
@@ -32669,7 +33291,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="138" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A12:C18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32742,85 +33364,90 @@
       </pivotArea>
     </chartFormat>
   </chartFormats>
-  <pivotHierarchies count="78">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
@@ -33218,13 +33845,13 @@
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <v>1.4611872146118721</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>1.3251533742331287</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="8">
         <v>1.4031413612565444</v>
       </c>
     </row>
@@ -33232,13 +33859,13 @@
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>1.4928774928774928</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>2.1724137931034484</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="8">
         <v>1.5892420537897312</v>
       </c>
     </row>
@@ -33246,13 +33873,13 @@
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="8">
         <v>1.904040404040404</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>1.9661016949152543</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="8">
         <v>1.9182879377431907</v>
       </c>
     </row>
@@ -33260,13 +33887,13 @@
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>1.9824561403508771</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>2.36</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="8">
         <v>2.0611111111111109</v>
       </c>
     </row>
@@ -33274,13 +33901,13 @@
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>1.9039735099337749</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="8">
         <v>2.1296296296296298</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="8">
         <v>1.9634146341463414</v>
       </c>
     </row>
@@ -33288,13 +33915,13 @@
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="8">
         <v>1.8850931677018634</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="8">
         <v>3.2105263157894739</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="8">
         <v>2.1870503597122304</v>
       </c>
     </row>
@@ -33302,13 +33929,13 @@
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="8">
         <v>1.7698270721526534</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="8">
         <v>2.096774193548387</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="8">
         <v>1.8514541387024608</v>
       </c>
     </row>
@@ -33947,6 +34574,504 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87B060B2-6AF9-40C7-B403-6CA72C692807}">
+  <dimension ref="A3:E29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.58981233243967823</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D4" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.5802139037433155</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D5" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.55524861878453047</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D6" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E6" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.65312499999999996</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D7" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.71944444444444444</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D8" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.7393617021276595</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D9" s="8">
+        <v>0</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.67929292929292928</v>
+      </c>
+      <c r="C10" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D10" s="8">
+        <v>-1</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.73262032085561501</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.76358695652173914</v>
+      </c>
+      <c r="C12" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D12" s="8">
+        <v>0</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.80294117647058827</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.74780701754385959</v>
+      </c>
+      <c r="C14" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D14" s="8">
+        <v>0</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.83114035087719296</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D16" s="8">
+        <v>1</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.85406698564593297</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.80835380835380832</v>
+      </c>
+      <c r="C18" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D18" s="8">
+        <v>1</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.81746031746031744</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D19" s="8">
+        <v>1</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0.83982683982683981</v>
+      </c>
+      <c r="C20" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D20" s="8">
+        <v>1</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B21" s="5">
+        <v>0.76249999999999996</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.80238095238095242</v>
+      </c>
+      <c r="C22" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D22" s="8">
+        <v>1</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.86190476190476195</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D23" s="8">
+        <v>1</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="5">
+        <v>0.83529411764705885</v>
+      </c>
+      <c r="C24" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D24" s="8">
+        <v>1</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D25" s="8">
+        <v>1</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0.83181818181818179</v>
+      </c>
+      <c r="C26" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D26" s="8">
+        <v>1</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.85681818181818181</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D27" s="8">
+        <v>1</v>
+      </c>
+      <c r="E27" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.90605427974947805</v>
+      </c>
+      <c r="C28" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D28" s="8">
+        <v>1</v>
+      </c>
+      <c r="E28" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0.77666435162218472</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="D29" s="8">
+        <v>0</v>
+      </c>
+      <c r="E29" s="8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting pivot="1" sqref="D4:D29">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="5Quarters" showValue="0">
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="-0.5"/>
+        <cfvo type="num" val="-0.01"/>
+        <cfvo type="num" val="0.01"/>
+        <cfvo type="num" val="0.5"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="E4:E29">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="5ArrowsGray" showValue="0">
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="-0.5"/>
+        <cfvo type="num" val="-0.01"/>
+        <cfvo type="num" val="0.01"/>
+        <cfvo type="num" val="0.5"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -34004,17 +35129,19 @@
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
+      <c r="B5" s="8"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
+      <c r="B6" s="8"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>1.2086570477247502</v>
       </c>
     </row>
@@ -34022,12 +35149,13 @@
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>0.56140350877192979</v>
       </c>
     </row>
@@ -34035,7 +35163,7 @@
       <c r="A10" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>3.4645390070921986</v>
       </c>
     </row>
@@ -34043,7 +35171,7 @@
       <c r="A11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="8">
         <v>1.4308426073131955</v>
       </c>
     </row>
@@ -34051,12 +35179,13 @@
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="B12" s="8"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="8">
         <v>1.1666666666666667</v>
       </c>
     </row>
@@ -34064,7 +35193,7 @@
       <c r="A14" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="8">
         <v>4.2163742690058479</v>
       </c>
     </row>
@@ -34072,7 +35201,7 @@
       <c r="A15" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="8">
         <v>2.6777546777546779</v>
       </c>
     </row>
@@ -34080,7 +35209,7 @@
       <c r="A16" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="8">
         <v>1.1880952380952381</v>
       </c>
     </row>
@@ -34088,7 +35217,7 @@
       <c r="A17" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="8">
         <v>1.0948616600790513</v>
       </c>
     </row>
@@ -34096,7 +35225,7 @@
       <c r="A18" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="8">
         <v>0.94680851063829785</v>
       </c>
     </row>
@@ -34104,12 +35233,13 @@
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="B19" s="8"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="8">
         <v>2.3026737967914439</v>
       </c>
     </row>
@@ -34117,7 +35247,7 @@
       <c r="A21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="8">
         <v>0.98565573770491799</v>
       </c>
     </row>
@@ -34125,7 +35255,7 @@
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="8">
         <v>1.6894683372841179</v>
       </c>
     </row>
@@ -34142,9 +35272,8 @@
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -34193,22 +35322,22 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="8">
         <v>4.5844155844155843</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>5.6934426229508199</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>9.9909836065573767</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <v>12.158196721311475</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="8">
         <v>12.445081967213115</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="8">
         <v>9.7461449498843482</v>
       </c>
     </row>
@@ -34252,7 +35381,7 @@
       <c r="F35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G35">
+      <c r="G35" s="8">
         <v>12.445081967213115</v>
       </c>
       <c r="J35" s="2" t="s">
@@ -34266,7 +35395,7 @@
       <c r="F36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G36">
+      <c r="G36" s="8">
         <v>12.158196721311475</v>
       </c>
       <c r="J36" s="2" t="s">
@@ -34280,7 +35409,7 @@
       <c r="F37" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G37">
+      <c r="G37" s="8">
         <v>9.9909836065573767</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -34294,7 +35423,7 @@
       <c r="F38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G38">
+      <c r="G38" s="8">
         <v>5.6934426229508199</v>
       </c>
     </row>
@@ -34302,7 +35431,7 @@
       <c r="F39" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G39">
+      <c r="G39" s="8">
         <v>4.5844155844155843</v>
       </c>
     </row>
@@ -34310,7 +35439,7 @@
       <c r="F40" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G40">
+      <c r="G40" s="8">
         <v>3.7236842105263159</v>
       </c>
     </row>
@@ -34318,7 +35447,7 @@
       <c r="F41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="8">
         <v>3.0649717514124295</v>
       </c>
     </row>
@@ -34326,7 +35455,7 @@
       <c r="F42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="8">
         <v>2.7666666666666666</v>
       </c>
     </row>
@@ -34334,7 +35463,7 @@
       <c r="F43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="8">
         <v>2.7333333333333334</v>
       </c>
     </row>
@@ -34342,7 +35471,7 @@
       <c r="F44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="8">
         <v>2.5181159420289854</v>
       </c>
     </row>
@@ -34350,7 +35479,7 @@
       <c r="F45" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="8">
         <v>1.8433734939759037</v>
       </c>
     </row>
@@ -34358,7 +35487,7 @@
       <c r="F46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="8">
         <v>1.6995073891625616</v>
       </c>
     </row>
@@ -34366,7 +35495,7 @@
       <c r="F47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="8">
         <v>1.1212121212121211</v>
       </c>
     </row>
@@ -34374,7 +35503,7 @@
       <c r="F48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="8">
         <v>0.91044776119402981</v>
       </c>
     </row>
@@ -34382,7 +35511,7 @@
       <c r="F49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="8">
         <v>0.83333333333333337</v>
       </c>
     </row>
@@ -34390,7 +35519,7 @@
       <c r="F50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="8">
         <v>0.77105263157894732</v>
       </c>
     </row>
@@ -34398,7 +35527,7 @@
       <c r="F51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="8">
         <v>0.70673076923076927</v>
       </c>
     </row>
@@ -34406,7 +35535,7 @@
       <c r="F52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G52">
+      <c r="G52" s="8">
         <v>1.834862385321101E-2</v>
       </c>
     </row>
@@ -34414,7 +35543,7 @@
       <c r="F53" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="8">
         <v>1.282051282051282E-2</v>
       </c>
     </row>
@@ -34422,7 +35551,7 @@
       <c r="F54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G54">
+      <c r="G54" s="8">
         <v>0</v>
       </c>
     </row>
@@ -34430,7 +35559,7 @@
       <c r="F55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G55">
+      <c r="G55" s="8">
         <v>0</v>
       </c>
     </row>
@@ -34438,7 +35567,7 @@
       <c r="F56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G56">
+      <c r="G56" s="8">
         <v>0</v>
       </c>
     </row>
@@ -34446,7 +35575,7 @@
       <c r="F57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="8">
         <v>0</v>
       </c>
     </row>
@@ -34454,7 +35583,7 @@
       <c r="F58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G58">
+      <c r="G58" s="8">
         <v>4.8117619639527653</v>
       </c>
     </row>
@@ -35136,7 +36265,7 @@
       <c r="A6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <v>7.333333333333333</v>
       </c>
     </row>
@@ -35144,7 +36273,7 @@
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>10.857142857142858</v>
       </c>
     </row>
@@ -35152,7 +36281,7 @@
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="8">
         <v>12.461538461538462</v>
       </c>
     </row>
@@ -35160,7 +36289,7 @@
       <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>9.2666666666666675</v>
       </c>
     </row>
@@ -35168,7 +36297,7 @@
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>6.7058823529411766</v>
       </c>
     </row>
@@ -35176,7 +36305,7 @@
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="8">
         <v>10</v>
       </c>
     </row>
@@ -35184,7 +36313,7 @@
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="8">
         <v>22.181818181818183</v>
       </c>
     </row>
@@ -35192,7 +36321,7 @@
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="8">
         <v>15.846153846153847</v>
       </c>
     </row>
@@ -35200,7 +36329,7 @@
       <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="8">
         <v>15.571428571428571</v>
       </c>
     </row>
@@ -35208,7 +36337,7 @@
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="8">
         <v>17.642857142857142</v>
       </c>
     </row>
@@ -35216,7 +36345,7 @@
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="8">
         <v>20.23076923076923</v>
       </c>
     </row>
@@ -35224,7 +36353,7 @@
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="8">
         <v>15.642857142857142</v>
       </c>
     </row>
@@ -35232,7 +36361,7 @@
       <c r="A18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="8">
         <v>16.866666666666667</v>
       </c>
     </row>
@@ -35240,7 +36369,7 @@
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="8">
         <v>19.23076923076923</v>
       </c>
     </row>
@@ -35248,7 +36377,7 @@
       <c r="A20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="8">
         <v>21.23076923076923</v>
       </c>
     </row>
@@ -35256,7 +36385,7 @@
       <c r="A21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="8">
         <v>37.75</v>
       </c>
     </row>
@@ -35264,7 +36393,7 @@
       <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B22">
+      <c r="B22" s="8">
         <v>32.222222222222221</v>
       </c>
     </row>
@@ -35272,7 +36401,7 @@
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B23">
+      <c r="B23" s="8">
         <v>25.833333333333332</v>
       </c>
     </row>
@@ -35280,7 +36409,7 @@
       <c r="A24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B24">
+      <c r="B24" s="8">
         <v>42.375</v>
       </c>
     </row>
@@ -35288,7 +36417,7 @@
       <c r="A25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B25">
+      <c r="B25" s="8">
         <v>24.166666666666668</v>
       </c>
     </row>
@@ -35296,7 +36425,7 @@
       <c r="A26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="8">
         <v>20.636363636363637</v>
       </c>
     </row>
@@ -35304,7 +36433,7 @@
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="8">
         <v>28.857142857142858</v>
       </c>
     </row>
@@ -35312,7 +36441,7 @@
       <c r="A28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="8">
         <v>31</v>
       </c>
     </row>
@@ -35320,7 +36449,7 @@
       <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B29">
+      <c r="B29" s="8">
         <v>30.333333333333332</v>
       </c>
     </row>
@@ -35328,7 +36457,7 @@
       <c r="A30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30">
+      <c r="B30" s="8">
         <v>41.5</v>
       </c>
     </row>
@@ -35336,7 +36465,7 @@
       <c r="A31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="8">
         <v>36</v>
       </c>
     </row>
@@ -35344,7 +36473,7 @@
       <c r="A32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B32">
+      <c r="B32" s="8">
         <v>18.508710801393729</v>
       </c>
     </row>
@@ -35380,11 +36509,15 @@
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="B2" s="8"/>
+      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>119</v>
       </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -35412,6 +36545,8 @@
       <c r="A6" s="3" t="s">
         <v>116</v>
       </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -35450,6 +36585,8 @@
       <c r="A10" s="3" t="s">
         <v>117</v>
       </c>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -35488,6 +36625,8 @@
       <c r="A14" s="3" t="s">
         <v>118</v>
       </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -35515,11 +36654,15 @@
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>119</v>
       </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -35547,6 +36690,8 @@
       <c r="A21" s="3" t="s">
         <v>116</v>
       </c>
+      <c r="B21" s="8"/>
+      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -35574,6 +36719,8 @@
       <c r="A24" s="3" t="s">
         <v>117</v>
       </c>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
@@ -35601,6 +36748,8 @@
       <c r="A27" s="3" t="s">
         <v>118</v>
       </c>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -35636,8 +36785,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35659,7 +36808,7 @@
       <c r="B2" s="5">
         <v>0.44833759590792838</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>22.692165044042653</v>
       </c>
     </row>
@@ -35670,7 +36819,7 @@
       <c r="B3" s="5">
         <v>0.43169697798441131</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>21.970163618864294</v>
       </c>
     </row>
@@ -35681,7 +36830,7 @@
       <c r="B4" s="5">
         <v>0.43795322234705342</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>23.093403598037433</v>
       </c>
     </row>
@@ -35692,7 +36841,7 @@
       <c r="B5" s="5">
         <v>0.36974938228026827</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>20.745169420330441</v>
       </c>
     </row>
@@ -35703,7 +36852,7 @@
       <c r="B6" s="5">
         <v>0.28947368421052633</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>16.462962962962962</v>
       </c>
     </row>
@@ -35714,7 +36863,7 @@
       <c r="B7" s="5">
         <v>0.42289579907310509</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>22.168771452626125</v>
       </c>
     </row>
@@ -35872,13 +37021,13 @@
       <c r="A6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <v>232</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="8">
         <v>70</v>
       </c>
     </row>
@@ -35886,13 +37035,13 @@
       <c r="A7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="8">
         <v>47</v>
       </c>
     </row>
@@ -35900,13 +37049,13 @@
       <c r="A8" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="8">
         <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="8">
         <v>37</v>
       </c>
     </row>
@@ -35914,13 +37063,13 @@
       <c r="A9" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="8">
         <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="8">
         <v>35</v>
       </c>
     </row>
@@ -35928,13 +37077,13 @@
       <c r="A10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="8">
         <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="8">
         <v>30</v>
       </c>
     </row>
@@ -35942,13 +37091,13 @@
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="8">
         <v>26</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="8">
         <v>25</v>
       </c>
     </row>
@@ -35956,13 +37105,13 @@
       <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="8">
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="8">
         <v>17</v>
       </c>
     </row>
@@ -35970,13 +37119,13 @@
       <c r="A13" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="8">
         <v>17</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="8">
         <v>15</v>
       </c>
     </row>
@@ -35984,13 +37133,13 @@
       <c r="A14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="8">
         <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="8">
         <v>12</v>
       </c>
     </row>
@@ -35998,13 +37147,13 @@
       <c r="A15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="8">
         <v>15</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="8">
         <v>9</v>
       </c>
     </row>
@@ -36012,13 +37161,13 @@
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="8">
         <v>524</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="8">
         <v>297</v>
       </c>
     </row>
@@ -36084,22 +37233,22 @@
       <c r="A4" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="8">
         <v>5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="8">
         <v>121</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="8">
         <v>2</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="8">
         <v>46</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="8">
         <v>7</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="8">
         <v>167</v>
       </c>
     </row>
@@ -36107,22 +37256,22 @@
       <c r="A5" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="8">
         <v>3</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>132</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="8">
         <v>6</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="8">
         <v>39</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="8">
         <v>9</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="8">
         <v>171</v>
       </c>
     </row>
@@ -36130,16 +37279,18 @@
       <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="8">
         <v>1</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>5</v>
       </c>
-      <c r="F6">
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8">
         <v>1</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="8">
         <v>5</v>
       </c>
     </row>
@@ -36147,22 +37298,22 @@
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="8">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>258</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="8">
         <v>8</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="8">
         <v>85</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="8">
         <v>17</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="8">
         <v>343</v>
       </c>
     </row>

--- a/project/stage03/analysis.xlsx
+++ b/project/stage03/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jantar\uni-data-warehouse\project\stage03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5540BB3B-B167-420C-9801-3F7FFF8E1AFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D88B6B9-DBBF-4A54-888D-5003CFA5D985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="4" activeTab="10" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="5" activeTab="8" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
   </bookViews>
   <sheets>
     <sheet name="RainVsPitStops" sheetId="1" r:id="rId1"/>
@@ -27,21 +27,21 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="132" r:id="rId12"/>
-    <pivotCache cacheId="135" r:id="rId13"/>
-    <pivotCache cacheId="138" r:id="rId14"/>
-    <pivotCache cacheId="141" r:id="rId15"/>
-    <pivotCache cacheId="144" r:id="rId16"/>
-    <pivotCache cacheId="147" r:id="rId17"/>
-    <pivotCache cacheId="150" r:id="rId18"/>
-    <pivotCache cacheId="153" r:id="rId19"/>
-    <pivotCache cacheId="156" r:id="rId20"/>
-    <pivotCache cacheId="159" r:id="rId21"/>
-    <pivotCache cacheId="162" r:id="rId22"/>
-    <pivotCache cacheId="165" r:id="rId23"/>
-    <pivotCache cacheId="168" r:id="rId24"/>
-    <pivotCache cacheId="171" r:id="rId25"/>
-    <pivotCache cacheId="174" r:id="rId26"/>
+    <pivotCache cacheId="0" r:id="rId12"/>
+    <pivotCache cacheId="1" r:id="rId13"/>
+    <pivotCache cacheId="2" r:id="rId14"/>
+    <pivotCache cacheId="3" r:id="rId15"/>
+    <pivotCache cacheId="4" r:id="rId16"/>
+    <pivotCache cacheId="5" r:id="rId17"/>
+    <pivotCache cacheId="6" r:id="rId18"/>
+    <pivotCache cacheId="7" r:id="rId19"/>
+    <pivotCache cacheId="8" r:id="rId20"/>
+    <pivotCache cacheId="9" r:id="rId21"/>
+    <pivotCache cacheId="10" r:id="rId22"/>
+    <pivotCache cacheId="11" r:id="rId23"/>
+    <pivotCache cacheId="12" r:id="rId24"/>
+    <pivotCache cacheId="13" r:id="rId25"/>
+    <pivotCache cacheId="17" r:id="rId26"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -3619,10 +3619,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>Calm</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Light Breeze</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Calm</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Moderate Breeze</c:v>
@@ -3637,10 +3637,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>1</c:v>
@@ -3684,10 +3684,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>Calm</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Light Breeze</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Calm</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Moderate Breeze</c:v>
@@ -3702,10 +3702,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>132</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>121</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>132</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>5</c:v>
@@ -3749,10 +3749,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>Calm</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Light Breeze</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Calm</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Moderate Breeze</c:v>
@@ -3767,10 +3767,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3811,10 +3811,10 @@
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>Calm</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>Light Breeze</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Calm</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>Moderate Breeze</c:v>
@@ -3829,10 +3829,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="1">
                   <c:v>46</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>39</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -27267,7 +27267,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650491319444" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7D06339B-CF30-4D37-AE3F-EEB11A431A55}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.69535613426" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7D06339B-CF30-4D37-AE3F-EEB11A431A55}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
     <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
@@ -28925,7 +28925,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="144" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:D12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -29187,7 +29187,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="165" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A1:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29364,350 +29364,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="171" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="3">
-    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
-    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
-    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="11">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="83">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="11" level="1">
-        <member name="[Dim Time].[Year].&amp;[2010]"/>
-        <member name="[Dim Time].[Year].&amp;[2011]"/>
-        <member name="[Dim Time].[Year].&amp;[2012]"/>
-        <member name="[Dim Time].[Year].&amp;[2013]"/>
-        <member name="[Dim Time].[Year].&amp;[2014]"/>
-        <member name="[Dim Time].[Year].&amp;[2015]"/>
-        <member name="[Dim Time].[Year].&amp;[2016]"/>
-        <member name="[Dim Time].[Year].&amp;[2017]"/>
-        <member name="[Dim Time].[Year].&amp;[2018]"/>
-        <member name="[Dim Time].[Year].&amp;[2019]"/>
-        <member name="[Dim Time].[Year].&amp;[2020]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" id="1" iMeasureHier="53">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="26"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="168" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -30054,8 +29711,351 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
+    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
+    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="11">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="11" level="1">
+        <member name="[Dim Time].[Year].&amp;[2010]"/>
+        <member name="[Dim Time].[Year].&amp;[2011]"/>
+        <member name="[Dim Time].[Year].&amp;[2012]"/>
+        <member name="[Dim Time].[Year].&amp;[2013]"/>
+        <member name="[Dim Time].[Year].&amp;[2014]"/>
+        <member name="[Dim Time].[Year].&amp;[2015]"/>
+        <member name="[Dim Time].[Year].&amp;[2016]"/>
+        <member name="[Dim Time].[Year].&amp;[2017]"/>
+        <member name="[Dim Time].[Year].&amp;[2018]"/>
+        <member name="[Dim Time].[Year].&amp;[2019]"/>
+        <member name="[Dim Time].[Year].&amp;[2020]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="53">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="26"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="174" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
   <location ref="A1:G7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -30076,8 +30076,8 @@
     </pivotField>
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="3">
+        <item x="0"/>
         <item x="1"/>
-        <item x="0"/>
         <item x="2"/>
       </items>
     </pivotField>
@@ -30310,7 +30310,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="135" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A3:B78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -30749,7 +30749,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB381D15-99CD-4BB2-BFAA-5B743EDB0261}" name="PivotTable1" cacheId="132" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB381D15-99CD-4BB2-BFAA-5B743EDB0261}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:E29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -30893,23 +30893,23 @@
     <dataField name="Constructor Reliability KPI Trend" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="2">
+    <conditionalFormat scope="data" priority="1">
+      <pivotAreas count="1">
+        <pivotArea outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
     <conditionalFormat scope="data" priority="2">
       <pivotAreas count="1">
         <pivotArea outline="0" fieldPosition="0">
           <references count="1">
             <reference field="4294967294" count="1" selected="0">
               <x v="2"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </pivotAreas>
-    </conditionalFormat>
-    <conditionalFormat scope="data" priority="1">
-      <pivotAreas count="1">
-        <pivotArea outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="3"/>
             </reference>
           </references>
         </pivotArea>
@@ -31020,7 +31020,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="141" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
   <location ref="A4:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -31579,7 +31579,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48529DB8-E948-488C-A714-CF42C15C483B}" name="PivotTable2" cacheId="153" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{48529DB8-E948-488C-A714-CF42C15C483B}" name="PivotTable2" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="F34:G58" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -31837,7 +31837,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="156" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
   <location ref="A3:G5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -32096,7 +32096,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="147" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
   <location ref="K5:U14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="5">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32453,7 +32453,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="150" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32719,7 +32719,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="159" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -33032,7 +33032,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="162" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A1:C29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -33291,7 +33291,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="138" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A12:C18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -33845,13 +33845,13 @@
       <c r="A6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>1.4611872146118721</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>1.3251533742331287</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6">
         <v>1.4031413612565444</v>
       </c>
     </row>
@@ -33859,13 +33859,13 @@
       <c r="A7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>1.4928774928774928</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>2.1724137931034484</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>1.5892420537897312</v>
       </c>
     </row>
@@ -33873,13 +33873,13 @@
       <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>1.904040404040404</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>1.9661016949152543</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8">
         <v>1.9182879377431907</v>
       </c>
     </row>
@@ -33887,13 +33887,13 @@
       <c r="A9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>1.9824561403508771</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>2.36</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9">
         <v>2.0611111111111109</v>
       </c>
     </row>
@@ -33901,13 +33901,13 @@
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>1.9039735099337749</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>2.1296296296296298</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10">
         <v>1.9634146341463414</v>
       </c>
     </row>
@@ -33915,13 +33915,13 @@
       <c r="A11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11">
         <v>1.8850931677018634</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>3.2105263157894739</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11">
         <v>2.1870503597122304</v>
       </c>
     </row>
@@ -33929,13 +33929,13 @@
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12">
         <v>1.7698270721526534</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12">
         <v>2.096774193548387</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12">
         <v>1.8514541387024608</v>
       </c>
     </row>
@@ -34613,13 +34613,13 @@
       <c r="B4" s="5">
         <v>0.58981233243967823</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>0.8</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>-1</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -34630,13 +34630,13 @@
       <c r="B5" s="5">
         <v>0.5802139037433155</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>0.8</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5">
         <v>-1</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5">
         <v>-1</v>
       </c>
     </row>
@@ -34647,13 +34647,13 @@
       <c r="B6" s="5">
         <v>0.55524861878453047</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>0.8</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6">
         <v>-1</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6">
         <v>-1</v>
       </c>
     </row>
@@ -34664,13 +34664,13 @@
       <c r="B7" s="5">
         <v>0.65312499999999996</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>0.8</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>-1</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -34681,13 +34681,13 @@
       <c r="B8" s="5">
         <v>0.71944444444444444</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8">
         <v>0.8</v>
       </c>
-      <c r="D8" s="8">
+      <c r="D8">
         <v>-1</v>
       </c>
-      <c r="E8" s="8">
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
@@ -34698,13 +34698,13 @@
       <c r="B9" s="5">
         <v>0.7393617021276595</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9">
         <v>0.8</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9">
         <v>0</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9">
         <v>1</v>
       </c>
     </row>
@@ -34715,13 +34715,13 @@
       <c r="B10" s="5">
         <v>0.67929292929292928</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10">
         <v>0.8</v>
       </c>
-      <c r="D10" s="8">
+      <c r="D10">
         <v>-1</v>
       </c>
-      <c r="E10" s="8">
+      <c r="E10">
         <v>-1</v>
       </c>
     </row>
@@ -34732,13 +34732,13 @@
       <c r="B11" s="5">
         <v>0.73262032085561501</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11">
         <v>0.8</v>
       </c>
-      <c r="D11" s="8">
+      <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11">
         <v>1</v>
       </c>
     </row>
@@ -34749,13 +34749,13 @@
       <c r="B12" s="5">
         <v>0.76358695652173914</v>
       </c>
-      <c r="C12" s="8">
+      <c r="C12">
         <v>0.8</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12">
         <v>0</v>
       </c>
-      <c r="E12" s="8">
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
@@ -34766,13 +34766,13 @@
       <c r="B13" s="5">
         <v>0.80294117647058827</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13">
         <v>0.8</v>
       </c>
-      <c r="D13" s="8">
+      <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="8">
+      <c r="E13">
         <v>1</v>
       </c>
     </row>
@@ -34783,13 +34783,13 @@
       <c r="B14" s="5">
         <v>0.74780701754385959</v>
       </c>
-      <c r="C14" s="8">
+      <c r="C14">
         <v>0.8</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14">
         <v>-1</v>
       </c>
     </row>
@@ -34800,13 +34800,13 @@
       <c r="B15" s="5">
         <v>0.83114035087719296</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15">
         <v>0.8</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15">
         <v>1</v>
       </c>
-      <c r="E15" s="8">
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
@@ -34817,13 +34817,13 @@
       <c r="B16" s="5">
         <v>0.82291666666666663</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16">
         <v>0.8</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16">
         <v>1</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16">
         <v>-1</v>
       </c>
     </row>
@@ -34834,13 +34834,13 @@
       <c r="B17" s="5">
         <v>0.85406698564593297</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17">
         <v>0.8</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17">
         <v>1</v>
       </c>
-      <c r="E17" s="8">
+      <c r="E17">
         <v>1</v>
       </c>
     </row>
@@ -34851,13 +34851,13 @@
       <c r="B18" s="5">
         <v>0.80835380835380832</v>
       </c>
-      <c r="C18" s="8">
+      <c r="C18">
         <v>0.8</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18">
         <v>1</v>
       </c>
-      <c r="E18" s="8">
+      <c r="E18">
         <v>-1</v>
       </c>
     </row>
@@ -34868,13 +34868,13 @@
       <c r="B19" s="5">
         <v>0.81746031746031744</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19">
         <v>0.8</v>
       </c>
-      <c r="D19" s="8">
+      <c r="D19">
         <v>1</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19">
         <v>1</v>
       </c>
     </row>
@@ -34885,13 +34885,13 @@
       <c r="B20" s="5">
         <v>0.83982683982683981</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20">
         <v>0.8</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20">
         <v>1</v>
       </c>
-      <c r="E20" s="8">
+      <c r="E20">
         <v>1</v>
       </c>
     </row>
@@ -34902,13 +34902,13 @@
       <c r="B21" s="5">
         <v>0.76249999999999996</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21">
         <v>0.8</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21">
         <v>0</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21">
         <v>-1</v>
       </c>
     </row>
@@ -34919,13 +34919,13 @@
       <c r="B22" s="5">
         <v>0.80238095238095242</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22">
         <v>0.8</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22">
         <v>1</v>
       </c>
-      <c r="E22" s="8">
+      <c r="E22">
         <v>1</v>
       </c>
     </row>
@@ -34936,13 +34936,13 @@
       <c r="B23" s="5">
         <v>0.86190476190476195</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23">
         <v>0.8</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23">
         <v>1</v>
       </c>
-      <c r="E23" s="8">
+      <c r="E23">
         <v>1</v>
       </c>
     </row>
@@ -34953,13 +34953,13 @@
       <c r="B24" s="5">
         <v>0.83529411764705885</v>
       </c>
-      <c r="C24" s="8">
+      <c r="C24">
         <v>0.8</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24">
         <v>1</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24">
         <v>-1</v>
       </c>
     </row>
@@ -34970,13 +34970,13 @@
       <c r="B25" s="5">
         <v>0.8727272727272728</v>
       </c>
-      <c r="C25" s="8">
+      <c r="C25">
         <v>0.8</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25">
         <v>1</v>
       </c>
-      <c r="E25" s="8">
+      <c r="E25">
         <v>1</v>
       </c>
     </row>
@@ -34987,13 +34987,13 @@
       <c r="B26" s="5">
         <v>0.83181818181818179</v>
       </c>
-      <c r="C26" s="8">
+      <c r="C26">
         <v>0.8</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26">
         <v>1</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26">
         <v>-1</v>
       </c>
     </row>
@@ -35004,13 +35004,13 @@
       <c r="B27" s="5">
         <v>0.85681818181818181</v>
       </c>
-      <c r="C27" s="8">
+      <c r="C27">
         <v>0.8</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27">
         <v>1</v>
       </c>
-      <c r="E27" s="8">
+      <c r="E27">
         <v>1</v>
       </c>
     </row>
@@ -35021,13 +35021,13 @@
       <c r="B28" s="5">
         <v>0.90605427974947805</v>
       </c>
-      <c r="C28" s="8">
+      <c r="C28">
         <v>0.8</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28">
         <v>1</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28">
         <v>1</v>
       </c>
     </row>
@@ -35038,13 +35038,13 @@
       <c r="B29" s="5">
         <v>0.77666435162218472</v>
       </c>
-      <c r="C29" s="8">
+      <c r="C29">
         <v>0.8</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29">
         <v>0</v>
       </c>
-      <c r="E29" s="8">
+      <c r="E29">
         <v>0</v>
       </c>
     </row>
@@ -35129,19 +35129,17 @@
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="8"/>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="8"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>1.2086570477247502</v>
       </c>
     </row>
@@ -35149,13 +35147,12 @@
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="8"/>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>0.56140350877192979</v>
       </c>
     </row>
@@ -35163,7 +35160,7 @@
       <c r="A10" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>3.4645390070921986</v>
       </c>
     </row>
@@ -35171,7 +35168,7 @@
       <c r="A11" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11">
         <v>1.4308426073131955</v>
       </c>
     </row>
@@ -35179,13 +35176,12 @@
       <c r="A12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="8"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13">
         <v>1.1666666666666667</v>
       </c>
     </row>
@@ -35193,7 +35189,7 @@
       <c r="A14" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14">
         <v>4.2163742690058479</v>
       </c>
     </row>
@@ -35201,7 +35197,7 @@
       <c r="A15" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15">
         <v>2.6777546777546779</v>
       </c>
     </row>
@@ -35209,7 +35205,7 @@
       <c r="A16" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16">
         <v>1.1880952380952381</v>
       </c>
     </row>
@@ -35217,7 +35213,7 @@
       <c r="A17" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17">
         <v>1.0948616600790513</v>
       </c>
     </row>
@@ -35225,7 +35221,7 @@
       <c r="A18" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18">
         <v>0.94680851063829785</v>
       </c>
     </row>
@@ -35233,13 +35229,12 @@
       <c r="A19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="8"/>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20">
         <v>2.3026737967914439</v>
       </c>
     </row>
@@ -35247,7 +35242,7 @@
       <c r="A21" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21">
         <v>0.98565573770491799</v>
       </c>
     </row>
@@ -35255,7 +35250,7 @@
       <c r="A22" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22">
         <v>1.6894683372841179</v>
       </c>
     </row>
@@ -35322,22 +35317,22 @@
       <c r="A5" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>4.5844155844155843</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>5.6934426229508199</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5">
         <v>9.9909836065573767</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5">
         <v>12.158196721311475</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5">
         <v>12.445081967213115</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5">
         <v>9.7461449498843482</v>
       </c>
     </row>
@@ -35381,7 +35376,7 @@
       <c r="F35" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="8">
+      <c r="G35">
         <v>12.445081967213115</v>
       </c>
       <c r="J35" s="2" t="s">
@@ -35395,7 +35390,7 @@
       <c r="F36" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G36" s="8">
+      <c r="G36">
         <v>12.158196721311475</v>
       </c>
       <c r="J36" s="2" t="s">
@@ -35409,7 +35404,7 @@
       <c r="F37" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G37" s="8">
+      <c r="G37">
         <v>9.9909836065573767</v>
       </c>
       <c r="J37" s="2" t="s">
@@ -35423,7 +35418,7 @@
       <c r="F38" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G38" s="8">
+      <c r="G38">
         <v>5.6934426229508199</v>
       </c>
     </row>
@@ -35431,7 +35426,7 @@
       <c r="F39" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G39" s="8">
+      <c r="G39">
         <v>4.5844155844155843</v>
       </c>
     </row>
@@ -35439,7 +35434,7 @@
       <c r="F40" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G40" s="8">
+      <c r="G40">
         <v>3.7236842105263159</v>
       </c>
     </row>
@@ -35447,7 +35442,7 @@
       <c r="F41" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G41" s="8">
+      <c r="G41">
         <v>3.0649717514124295</v>
       </c>
     </row>
@@ -35455,7 +35450,7 @@
       <c r="F42" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G42" s="8">
+      <c r="G42">
         <v>2.7666666666666666</v>
       </c>
     </row>
@@ -35463,7 +35458,7 @@
       <c r="F43" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="G43" s="8">
+      <c r="G43">
         <v>2.7333333333333334</v>
       </c>
     </row>
@@ -35471,7 +35466,7 @@
       <c r="F44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G44" s="8">
+      <c r="G44">
         <v>2.5181159420289854</v>
       </c>
     </row>
@@ -35479,7 +35474,7 @@
       <c r="F45" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G45" s="8">
+      <c r="G45">
         <v>1.8433734939759037</v>
       </c>
     </row>
@@ -35487,7 +35482,7 @@
       <c r="F46" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G46" s="8">
+      <c r="G46">
         <v>1.6995073891625616</v>
       </c>
     </row>
@@ -35495,7 +35490,7 @@
       <c r="F47" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G47" s="8">
+      <c r="G47">
         <v>1.1212121212121211</v>
       </c>
     </row>
@@ -35503,7 +35498,7 @@
       <c r="F48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="G48" s="8">
+      <c r="G48">
         <v>0.91044776119402981</v>
       </c>
     </row>
@@ -35511,7 +35506,7 @@
       <c r="F49" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G49" s="8">
+      <c r="G49">
         <v>0.83333333333333337</v>
       </c>
     </row>
@@ -35519,7 +35514,7 @@
       <c r="F50" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="G50" s="8">
+      <c r="G50">
         <v>0.77105263157894732</v>
       </c>
     </row>
@@ -35527,7 +35522,7 @@
       <c r="F51" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G51" s="8">
+      <c r="G51">
         <v>0.70673076923076927</v>
       </c>
     </row>
@@ -35535,7 +35530,7 @@
       <c r="F52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G52" s="8">
+      <c r="G52">
         <v>1.834862385321101E-2</v>
       </c>
     </row>
@@ -35543,7 +35538,7 @@
       <c r="F53" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="8">
+      <c r="G53">
         <v>1.282051282051282E-2</v>
       </c>
     </row>
@@ -35551,7 +35546,7 @@
       <c r="F54" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G54" s="8">
+      <c r="G54">
         <v>0</v>
       </c>
     </row>
@@ -35559,7 +35554,7 @@
       <c r="F55" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G55" s="8">
+      <c r="G55">
         <v>0</v>
       </c>
     </row>
@@ -35567,7 +35562,7 @@
       <c r="F56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G56" s="8">
+      <c r="G56">
         <v>0</v>
       </c>
     </row>
@@ -35575,7 +35570,7 @@
       <c r="F57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G57" s="8">
+      <c r="G57">
         <v>0</v>
       </c>
     </row>
@@ -35583,7 +35578,7 @@
       <c r="F58" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G58" s="8">
+      <c r="G58">
         <v>4.8117619639527653</v>
       </c>
     </row>
@@ -36265,7 +36260,7 @@
       <c r="A6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>7.333333333333333</v>
       </c>
     </row>
@@ -36273,7 +36268,7 @@
       <c r="A7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>10.857142857142858</v>
       </c>
     </row>
@@ -36281,7 +36276,7 @@
       <c r="A8" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>12.461538461538462</v>
       </c>
     </row>
@@ -36289,7 +36284,7 @@
       <c r="A9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>9.2666666666666675</v>
       </c>
     </row>
@@ -36297,7 +36292,7 @@
       <c r="A10" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>6.7058823529411766</v>
       </c>
     </row>
@@ -36305,7 +36300,7 @@
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11">
         <v>10</v>
       </c>
     </row>
@@ -36313,7 +36308,7 @@
       <c r="A12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12">
         <v>22.181818181818183</v>
       </c>
     </row>
@@ -36321,7 +36316,7 @@
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13">
         <v>15.846153846153847</v>
       </c>
     </row>
@@ -36329,7 +36324,7 @@
       <c r="A14" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14">
         <v>15.571428571428571</v>
       </c>
     </row>
@@ -36337,7 +36332,7 @@
       <c r="A15" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15">
         <v>17.642857142857142</v>
       </c>
     </row>
@@ -36345,7 +36340,7 @@
       <c r="A16" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16">
         <v>20.23076923076923</v>
       </c>
     </row>
@@ -36353,7 +36348,7 @@
       <c r="A17" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="8">
+      <c r="B17">
         <v>15.642857142857142</v>
       </c>
     </row>
@@ -36361,7 +36356,7 @@
       <c r="A18" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B18" s="8">
+      <c r="B18">
         <v>16.866666666666667</v>
       </c>
     </row>
@@ -36369,7 +36364,7 @@
       <c r="A19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B19" s="8">
+      <c r="B19">
         <v>19.23076923076923</v>
       </c>
     </row>
@@ -36377,7 +36372,7 @@
       <c r="A20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B20" s="8">
+      <c r="B20">
         <v>21.23076923076923</v>
       </c>
     </row>
@@ -36385,7 +36380,7 @@
       <c r="A21" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="8">
+      <c r="B21">
         <v>37.75</v>
       </c>
     </row>
@@ -36393,7 +36388,7 @@
       <c r="A22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B22" s="8">
+      <c r="B22">
         <v>32.222222222222221</v>
       </c>
     </row>
@@ -36401,7 +36396,7 @@
       <c r="A23" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B23" s="8">
+      <c r="B23">
         <v>25.833333333333332</v>
       </c>
     </row>
@@ -36409,7 +36404,7 @@
       <c r="A24" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B24" s="8">
+      <c r="B24">
         <v>42.375</v>
       </c>
     </row>
@@ -36417,7 +36412,7 @@
       <c r="A25" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B25" s="8">
+      <c r="B25">
         <v>24.166666666666668</v>
       </c>
     </row>
@@ -36425,7 +36420,7 @@
       <c r="A26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B26" s="8">
+      <c r="B26">
         <v>20.636363636363637</v>
       </c>
     </row>
@@ -36433,7 +36428,7 @@
       <c r="A27" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B27" s="8">
+      <c r="B27">
         <v>28.857142857142858</v>
       </c>
     </row>
@@ -36441,7 +36436,7 @@
       <c r="A28" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B28" s="8">
+      <c r="B28">
         <v>31</v>
       </c>
     </row>
@@ -36449,7 +36444,7 @@
       <c r="A29" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="8">
+      <c r="B29">
         <v>30.333333333333332</v>
       </c>
     </row>
@@ -36457,7 +36452,7 @@
       <c r="A30" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="8">
+      <c r="B30">
         <v>41.5</v>
       </c>
     </row>
@@ -36465,7 +36460,7 @@
       <c r="A31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B31" s="8">
+      <c r="B31">
         <v>36</v>
       </c>
     </row>
@@ -36473,7 +36468,7 @@
       <c r="A32" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B32" s="8">
+      <c r="B32">
         <v>18.508710801393729</v>
       </c>
     </row>
@@ -36509,15 +36504,11 @@
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
@@ -36545,8 +36536,6 @@
       <c r="A6" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
@@ -36585,8 +36574,6 @@
       <c r="A10" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
@@ -36625,8 +36612,6 @@
       <c r="A14" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
@@ -36654,15 +36639,11 @@
       <c r="A17" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
@@ -36690,8 +36671,6 @@
       <c r="A21" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
@@ -36719,8 +36698,6 @@
       <c r="A24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B24" s="8"/>
-      <c r="C24" s="8"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
@@ -36748,8 +36725,6 @@
       <c r="A27" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
@@ -36808,7 +36783,7 @@
       <c r="B2" s="5">
         <v>0.44833759590792838</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2">
         <v>22.692165044042653</v>
       </c>
     </row>
@@ -36819,7 +36794,7 @@
       <c r="B3" s="5">
         <v>0.43169697798441131</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3">
         <v>21.970163618864294</v>
       </c>
     </row>
@@ -36830,7 +36805,7 @@
       <c r="B4" s="5">
         <v>0.43795322234705342</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>23.093403598037433</v>
       </c>
     </row>
@@ -36841,7 +36816,7 @@
       <c r="B5" s="5">
         <v>0.36974938228026827</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>20.745169420330441</v>
       </c>
     </row>
@@ -36852,7 +36827,7 @@
       <c r="B6" s="5">
         <v>0.28947368421052633</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>16.462962962962962</v>
       </c>
     </row>
@@ -36863,7 +36838,7 @@
       <c r="B7" s="5">
         <v>0.42289579907310509</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>22.168771452626125</v>
       </c>
     </row>
@@ -37021,13 +36996,13 @@
       <c r="A6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>232</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <v>70</v>
       </c>
     </row>
@@ -37035,13 +37010,13 @@
       <c r="A7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>70</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7">
         <v>47</v>
       </c>
     </row>
@@ -37049,13 +37024,13 @@
       <c r="A8" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8">
         <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8">
         <v>37</v>
       </c>
     </row>
@@ -37063,13 +37038,13 @@
       <c r="A9" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="8">
+      <c r="B9">
         <v>33</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9">
         <v>35</v>
       </c>
     </row>
@@ -37077,13 +37052,13 @@
       <c r="A10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="B10" s="8">
+      <c r="B10">
         <v>31</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10">
         <v>30</v>
       </c>
     </row>
@@ -37091,13 +37066,13 @@
       <c r="A11" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B11" s="8">
+      <c r="B11">
         <v>26</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11">
         <v>25</v>
       </c>
     </row>
@@ -37105,13 +37080,13 @@
       <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="8">
+      <c r="B12">
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12">
         <v>17</v>
       </c>
     </row>
@@ -37119,13 +37094,13 @@
       <c r="A13" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B13">
         <v>17</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13">
         <v>15</v>
       </c>
     </row>
@@ -37133,13 +37108,13 @@
       <c r="A14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14">
         <v>16</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14">
         <v>12</v>
       </c>
     </row>
@@ -37147,13 +37122,13 @@
       <c r="A15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B15">
         <v>15</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="G15" s="8">
+      <c r="G15">
         <v>9</v>
       </c>
     </row>
@@ -37161,13 +37136,13 @@
       <c r="A16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B16">
         <v>524</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16">
         <v>297</v>
       </c>
     </row>
@@ -37231,48 +37206,48 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B4" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C4" s="8">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="D4" s="8">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E4" s="8">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="F4" s="8">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G4" s="8">
-        <v>167</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="8">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D5" s="8">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E5" s="8">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F5" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5" s="8">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">

--- a/project/stage03/analysis.xlsx
+++ b/project/stage03/analysis.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jantar\uni-data-warehouse\project\stage03\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D88B6B9-DBBF-4A54-888D-5003CFA5D985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C92CF5-503A-455E-B9BE-7E072D2C452B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="5" activeTab="8" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="879" firstSheet="5" activeTab="12" xr2:uid="{5D7D4CC1-6A94-48C8-A9CB-AB14AE6EE489}"/>
   </bookViews>
   <sheets>
     <sheet name="RainVsPitStops" sheetId="1" r:id="rId1"/>
@@ -23,25 +23,29 @@
     <sheet name="Top 10 reasons for Mechanical" sheetId="9" r:id="rId8"/>
     <sheet name="Podium from in or out weather" sheetId="10" r:id="rId9"/>
     <sheet name="Average Race Time in Autodromo " sheetId="11" r:id="rId10"/>
-    <sheet name="Sheet1" sheetId="12" r:id="rId11"/>
+    <sheet name="KPI" sheetId="12" r:id="rId11"/>
+    <sheet name="KPI Colors" sheetId="13" r:id="rId12"/>
+    <sheet name="Sheet1" sheetId="14" r:id="rId13"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId12"/>
-    <pivotCache cacheId="1" r:id="rId13"/>
-    <pivotCache cacheId="2" r:id="rId14"/>
-    <pivotCache cacheId="3" r:id="rId15"/>
-    <pivotCache cacheId="4" r:id="rId16"/>
-    <pivotCache cacheId="5" r:id="rId17"/>
-    <pivotCache cacheId="6" r:id="rId18"/>
-    <pivotCache cacheId="7" r:id="rId19"/>
-    <pivotCache cacheId="8" r:id="rId20"/>
-    <pivotCache cacheId="9" r:id="rId21"/>
-    <pivotCache cacheId="10" r:id="rId22"/>
-    <pivotCache cacheId="11" r:id="rId23"/>
-    <pivotCache cacheId="12" r:id="rId24"/>
-    <pivotCache cacheId="13" r:id="rId25"/>
-    <pivotCache cacheId="17" r:id="rId26"/>
+    <pivotCache cacheId="0" r:id="rId14"/>
+    <pivotCache cacheId="1" r:id="rId15"/>
+    <pivotCache cacheId="2" r:id="rId16"/>
+    <pivotCache cacheId="3" r:id="rId17"/>
+    <pivotCache cacheId="4" r:id="rId18"/>
+    <pivotCache cacheId="5" r:id="rId19"/>
+    <pivotCache cacheId="6" r:id="rId20"/>
+    <pivotCache cacheId="7" r:id="rId21"/>
+    <pivotCache cacheId="8" r:id="rId22"/>
+    <pivotCache cacheId="9" r:id="rId23"/>
+    <pivotCache cacheId="10" r:id="rId24"/>
+    <pivotCache cacheId="11" r:id="rId25"/>
+    <pivotCache cacheId="12" r:id="rId26"/>
+    <pivotCache cacheId="13" r:id="rId27"/>
+    <pivotCache cacheId="14" r:id="rId28"/>
+    <pivotCache cacheId="15" r:id="rId29"/>
+    <pivotCache cacheId="86" r:id="rId30"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -60,7 +64,7 @@
   <metadataTypes count="1">
     <metadataType name="XLMDX" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <metadataStrings count="13">
+  <metadataStrings count="14">
     <s v="localhost FormulaCube"/>
     <s v="{[Dim Time].[Year].&amp;[2018],[Dim Time].[Year].&amp;[2019],[Dim Time].[Year].&amp;[2020],[Dim Time].[Year].&amp;[2021],[Dim Time].[Year].&amp;[2022],[Dim Time].[Year].&amp;[2023]}"/>
     <s v="{[Dim Circuit].[Continent].&amp;[Europe]}"/>
@@ -74,8 +78,9 @@
     <s v="{[Dim Time].[Year].&amp;[2010],[Dim Time].[Year].&amp;[2011],[Dim Time].[Year].&amp;[2012],[Dim Time].[Year].&amp;[2013],[Dim Time].[Year].&amp;[2014],[Dim Time].[Year].&amp;[2015],[Dim Time].[Year].&amp;[2016],[Dim Time].[Year].&amp;[2017],[Dim Time].[Year].&amp;[2018],[Dim Time].[Year].&amp;[2019],[Dim Time].[Year].&amp;[2020]}"/>
     <s v="{[Dim Constructor].[Continent].&amp;[Europe]}"/>
     <s v="{[Dim Circuit].[Circuit Name].&amp;[Autodromo Nazionale di Monza]}"/>
+    <s v="{[Dim Time].[Year].&amp;[2000],[Dim Time].[Year].&amp;[2001],[Dim Time].[Year].&amp;[2002],[Dim Time].[Year].&amp;[2003],[Dim Time].[Year].&amp;[2004],[Dim Time].[Year].&amp;[2005],[Dim Time].[Year].&amp;[2006],[Dim Time].[Year].&amp;[2007],[Dim Time].[Year].&amp;[2008],[Dim Time].[Year].&amp;[2009],[Dim Time].[Year].&amp;[2010],[Dim Time].[Year].&amp;[2011],[Dim Time].[Year].&amp;[2012],[Dim Time].[Year].&amp;[2013],[Dim Time].[Year].&amp;[2014],[Dim Time].[Year].&amp;[2015],[Dim Time].[Year].&amp;[2016],[Dim Time].[Year].&amp;[2017],[Dim Time].[Year].&amp;[2018],[Dim Time].[Year].&amp;[2019],[Dim Time].[Year].&amp;[2020],[Dim Time].[Year].&amp;[2021],[Dim Time].[Year].&amp;[2022],[Dim Time].[Year].&amp;[2023],[Dim Time].[Year].&amp;[2024]}"/>
   </metadataStrings>
-  <mdxMetadata count="12">
+  <mdxMetadata count="13">
     <mdx n="0" f="s">
       <ms ns="1" c="0"/>
     </mdx>
@@ -112,8 +117,11 @@
     <mdx n="0" f="s">
       <ms ns="12" c="0"/>
     </mdx>
+    <mdx n="0" f="s">
+      <ms ns="13" c="0"/>
+    </mdx>
   </mdxMetadata>
-  <valueMetadata count="12">
+  <valueMetadata count="13">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -150,12 +158,15 @@
     <bk>
       <rc t="1" v="11"/>
     </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="233">
   <si>
     <t>AveragePitStopsCount</t>
   </si>
@@ -839,6 +850,21 @@
   </si>
   <si>
     <t>Constructor Reliability KPI Trend</t>
+  </si>
+  <si>
+    <t>Accident/Incident</t>
+  </si>
+  <si>
+    <t>Driver Issue</t>
+  </si>
+  <si>
+    <t>Pre-Race/Qualification</t>
+  </si>
+  <si>
+    <t>Race Outcome</t>
+  </si>
+  <si>
+    <t>Sporting/Regulatory</t>
   </si>
 </sst>
 </file>
@@ -5045,6 +5071,425 @@
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pl-PL"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[analysis.xlsx]Sheet1!PivotTable1</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pl-PL"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pl-PL"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:ofPieChart>
+        <c:ofPieType val="pie"/>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="6"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Accident/Incident</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Driver Issue</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Mechanical Failure</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Pre-Race/Qualification</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Race Outcome</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Sporting/Regulatory</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>2781</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6696</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1356</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>15441</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>417</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1C22-4AD5-BA83-D322A2EE414B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:secondPieSize val="75"/>
+        <c:serLines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="35000"/>
+                  <a:lumOff val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:serLines>
+      </c:ofPieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -19303,6 +19748,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -21634,6 +22119,525 @@
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style13.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -25834,6 +26838,47 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>753717</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>44725</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>289892</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>173934</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{161EB8BB-2473-5D41-0EA1-BE413F019E47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -26235,1039 +27280,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650479166667" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{EDAF3AB4-F84F-4D58-B645-530C9DA3FC38}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" numFmtId="0" hierarchy="78" level="32767"/>
-    <cacheField name="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" numFmtId="0" hierarchy="79" level="32767"/>
-    <cacheField name="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" numFmtId="0" hierarchy="80" level="32767"/>
-    <cacheField name="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" numFmtId="0" hierarchy="81" level="32767"/>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="25">
-        <s v="[Dim Time].[Year].&amp;[2000]" c="2000"/>
-        <s v="[Dim Time].[Year].&amp;[2001]" c="2001"/>
-        <s v="[Dim Time].[Year].&amp;[2002]" c="2002"/>
-        <s v="[Dim Time].[Year].&amp;[2003]" c="2003"/>
-        <s v="[Dim Time].[Year].&amp;[2004]" c="2004"/>
-        <s v="[Dim Time].[Year].&amp;[2005]" c="2005"/>
-        <s v="[Dim Time].[Year].&amp;[2006]" c="2006"/>
-        <s v="[Dim Time].[Year].&amp;[2007]" c="2007"/>
-        <s v="[Dim Time].[Year].&amp;[2008]" c="2008"/>
-        <s v="[Dim Time].[Year].&amp;[2009]" c="2009"/>
-        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
-        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
-        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
-        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
-        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
-        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
-        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
-        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" iconSet="8" displayFolder="" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" iconSet="5" displayFolder="" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.65048715278" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3962C440-443E-4D75-B22B-0E43959F42B2}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="4">
-    <cacheField name="[Degenerate Details].[Grid Position].[Grid Position]" caption="Grid Position" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems count="30">
-        <s v="[Degenerate Details].[Grid Position].&amp;[1]" c="1"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[2]" c="2"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[3]" c="3"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[4]" c="4"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[5]" c="5"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[6]" c="6"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[7]" c="7"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[8]" c="8"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[9]" c="9"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[10]" c="10"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[11]" c="11"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[12]" c="12"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[13]" c="13"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[14]" c="14"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[15]" c="15"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[16]" c="16"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[17]" c="17"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[18]" c="18"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[19]" c="19"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[20]" c="20"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[21]" c="21"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[22]" c="22"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[23]" c="23"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[24]" c="24"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[25]" c="25"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[26]" c="26"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[28]" u="1" c="28"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[29]" u="1" c="29"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[31]" u="1" c="31"/>
-        <s v="[Degenerate Details].[Grid Position].&amp;[32]" u="1" c="32"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
-    <cacheField name="[Dim Race].[Race Name Official].[Race Name Official]" caption="Race Name Official" numFmtId="0" hierarchy="22" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650487962965" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5251863D-400F-43FD-A0F1-A4BBAAFEDC07}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
-      <sharedItems count="2">
-        <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
-        <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Weather].[Track Temp Category].[Track Temp Category]" caption="Track Temp Category" numFmtId="0" hierarchy="42" level="1">
-      <sharedItems count="4">
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Cool Track]" c="Cool Track"/>
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Hot Track]" c="Hot Track"/>
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Optimal Track]" c="Optimal Track"/>
-        <s v="[Dim Weather].[Track Temp Category].&amp;[Very Hot Track]" c="Very Hot Track"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Weather].[Wind Speed Category].[Wind Speed Category]" caption="Wind Speed Category" numFmtId="0" hierarchy="44" level="1">
-      <sharedItems count="3">
-        <s v="[Dim Weather].[Wind Speed Category].&amp;[Calm]" c="Calm"/>
-        <s v="[Dim Weather].[Wind Speed Category].&amp;[Light Breeze]" c="Light Breeze"/>
-        <s v="[Dim Weather].[Wind Speed Category].&amp;[Moderate Breeze]" c="Moderate Breeze"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
-    <cacheField name="[Measures].[Finish Percentage]" caption="Finish Percentage" numFmtId="0" hierarchy="74" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650488657404" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{91EA7F40-35C5-4637-AD47-C1EF62F40064}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Degenerate Details].[Age Group].[Age Group]" caption="Age Group" numFmtId="0" hierarchy="1" level="1">
-      <sharedItems count="5">
-        <s v="[Degenerate Details].[Age Group].&amp;[20-25]" c="20-25"/>
-        <s v="[Degenerate Details].[Age Group].&amp;[26-30]" c="26-30"/>
-        <s v="[Degenerate Details].[Age Group].&amp;[31-35]" c="31-35"/>
-        <s v="[Degenerate Details].[Age Group].&amp;[Over 35]" c="Over 35"/>
-        <s v="[Degenerate Details].[Age Group].&amp;[Under 20]" c="Under 20"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
-    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650489583335" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{22B37FF6-6A8A-4281-AC48-8C27DD0DC8A1}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="6">
-    <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
-      <sharedItems count="10">
-        <s v="[Dim Status].[Status Description].&amp;[Axle]" c="Axle"/>
-        <s v="[Dim Status].[Status Description].&amp;[Brakes]" c="Brakes"/>
-        <s v="[Dim Status].[Status Description].&amp;[Clutch]" c="Clutch"/>
-        <s v="[Dim Status].[Status Description].&amp;[Engine]" c="Engine"/>
-        <s v="[Dim Status].[Status Description].&amp;[Gearbox]" c="Gearbox"/>
-        <s v="[Dim Status].[Status Description].&amp;[Ignition]" c="Ignition"/>
-        <s v="[Dim Status].[Status Description].&amp;[Oil leak]" c="Oil leak"/>
-        <s v="[Dim Status].[Status Description].&amp;[Overheating]" c="Overheating"/>
-        <s v="[Dim Status].[Status Description].&amp;[Suspension]" c="Suspension"/>
-        <s v="[Dim Status].[Status Description].&amp;[Transmission]" c="Transmission"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Status].[Status Category].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="25" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Constructor].[Country Name].[Country Name]" caption="Country Name" numFmtId="0" hierarchy="13" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Constructor].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650490509259" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{8FE8892F-6B13-44C4-9323-FDA7B9542767}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
-      <sharedItems count="10">
-        <s v="[Dim Status].[Status Description].&amp;[Brakes]" c="Brakes"/>
-        <s v="[Dim Status].[Status Description].&amp;[Electrical]" c="Electrical"/>
-        <s v="[Dim Status].[Status Description].&amp;[Engine]" c="Engine"/>
-        <s v="[Dim Status].[Status Description].&amp;[Gearbox]" c="Gearbox"/>
-        <s v="[Dim Status].[Status Description].&amp;[Hydraulics]" c="Hydraulics"/>
-        <s v="[Dim Status].[Status Description].&amp;[Mechanical]" c="Mechanical"/>
-        <s v="[Dim Status].[Status Description].&amp;[Power Unit]" c="Power Unit"/>
-        <s v="[Dim Status].[Status Description].&amp;[Puncture]" c="Puncture"/>
-        <s v="[Dim Status].[Status Description].&amp;[Suspension]" c="Suspension"/>
-        <s v="[Dim Status].[Status Description].&amp;[Wheel]" c="Wheel"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Status].[Status Category].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="25" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Constructor].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="12" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.69535613426" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7D06339B-CF30-4D37-AE3F-EEB11A431A55}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481284374997" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7D06339B-CF30-4D37-AE3F-EEB11A431A55}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="5">
     <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
@@ -27400,6 +27413,192 @@
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" iconSet="10" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" iconSet="3" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481313078701" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{70BBC5B2-939A-459F-88F4-8193C9E44ED3}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Driver].[Full Name].[Full Name]" caption="Full Name" numFmtId="0" hierarchy="19" level="1">
+      <sharedItems count="9">
+        <s v="[Dim Driver].[Full Name].&amp;[Carlos Sainz]" c="Carlos Sainz"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Charles Leclerc]" c="Charles Leclerc"/>
+        <s v="[Dim Driver].[Full Name].&amp;[George Russell]" c="George Russell"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Kimi Räikkönen]" c="Kimi Räikkönen"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Lando Norris]" c="Lando Norris"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Lewis Hamilton]" c="Lewis Hamilton"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Max Verstappen]" c="Max Verstappen"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Sebastian Vettel]" c="Sebastian Vettel"/>
+        <s v="[Dim Driver].[Full Name].&amp;[Valtteri Bottas]" c="Valtteri Bottas"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Driver].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="16" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
+    <cacheField name="[Dim Race].[Year Season].[Year Season]" caption="Year Season" numFmtId="0" hierarchy="24" level="1">
+      <sharedItems count="7">
+        <s v="[Dim Race].[Year Season].&amp;[2018]" c="2018"/>
+        <s v="[Dim Race].[Year Season].&amp;[2019]" c="2019"/>
+        <s v="[Dim Race].[Year Season].&amp;[2020]" c="2020"/>
+        <s v="[Dim Race].[Year Season].&amp;[2021]" c="2021"/>
+        <s v="[Dim Race].[Year Season].&amp;[2022]" c="2022"/>
+        <s v="[Dim Race].[Year Season].&amp;[2023]" c="2023"/>
+        <s v="[Dim Race].[Year Season].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
   </cacheHierarchies>
@@ -27438,8 +27637,548 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650480324075" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{125F41B5-3B3C-4D18-ADBF-159F41F79641}">
+<file path=xl/pivotCache/pivotCacheDefinition11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481316087964" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{19EFFABB-3DF1-4D82-9260-5ADF45140058}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="7">
+    <cacheField name="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" numFmtId="0" hierarchy="68" level="32767"/>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Year]" caption="Year" numFmtId="0" hierarchy="36" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2023]" c="2023"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="36" level="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Month]" caption="Month" numFmtId="0" hierarchy="36" level="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Day Of Month]" caption="Day Of Month" numFmtId="0" hierarchy="36" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
+      <sharedItems count="3">
+        <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
+        <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
+        <s v="[Dim Weather].[Did Rain Occur].[All].UNKNOWNMEMBER" u="1" c="Unknown"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+        <fieldUsage x="2"/>
+        <fieldUsage x="3"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.48131909722" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{83FC3B7F-BBEF-4612-AC70-0D06FDFFB172}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="7">
+    <cacheField name="[Dim Circuit].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="7" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" numFmtId="0" hierarchy="69" level="32767"/>
+    <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
+      <sharedItems count="30">
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Charade Circuit]" c="Charade Circuit"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Nevers Magny-Cours]" c="Circuit de Nevers Magny-Cours"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Spa-Francorchamps]" c="Circuit de Spa-Francorchamps"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Paul Ricard]" c="Circuit Paul Ricard"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Dijon-Prenois]" c="Dijon-Prenois"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Hockenheimring]" c="Hockenheimring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Nivelles-Baulers]" c="Nivelles-Baulers"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Nürburgring]" c="Nürburgring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Red Bull Ring]" c="Red Bull Ring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Reims-Gueux]" c="Reims-Gueux"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Rouen-Les-Essarts]" c="Rouen-Les-Essarts"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Zolder]" c="Zolder"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Aintree]" u="1" c="Aintree"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Enzo e Dino Ferrari]" u="1" c="Autodromo Enzo e Dino Ferrari"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Nazionale di Monza]" u="1" c="Autodromo Nazionale di Monza"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Autódromo do Estoril]" u="1" c="Autódromo do Estoril"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Brands Hatch]" u="1" c="Brands Hatch"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Bremgarten]" u="1" c="Circuit Bremgarten"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Barcelona-Catalunya]" u="1" c="Circuit de Barcelona-Catalunya"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Monaco]" u="1" c="Circuit de Monaco"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Pedralbes]" u="1" c="Circuit de Pedralbes"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Park Zandvoort]" u="1" c="Circuit Park Zandvoort"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuito de Jerez]" u="1" c="Circuito de Jerez"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Donington Park]" u="1" c="Donington Park"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Hungaroring]" u="1" c="Hungaroring"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Jarama]" u="1" c="Jarama"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Scandinavian Raceway]" u="1" c="Scandinavian Raceway"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Silverstone Circuit]" u="1" c="Silverstone Circuit"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Sochi Autodrom]" u="1" c="Sochi Autodrom"/>
+        <s v="[Dim Circuit].[Circuit Name].&amp;[Valencia Street Circuit]" u="1" c="Valencia Street Circuit"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Continent]" caption="Continent" numFmtId="0" hierarchy="10" level="1">
+      <sharedItems count="1">
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe]" c="Europe"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Country Name]" caption="Country Name" numFmtId="0" hierarchy="10" level="2">
+      <sharedItems count="4">
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria]" c="Austria"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium]" c="Belgium"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France]" c="France"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany]" c="Germany"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Location City]" caption="Location City" numFmtId="0" hierarchy="10" level="3">
+      <sharedItems count="12">
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria].&amp;[Spielberg]" c="Spielberg"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Brussels]" c="Brussels"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Heusden-Zolder]" c="Heusden-Zolder"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Spa]" c="Spa"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Clermont-Ferrand]" c="Clermont-Ferrand"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Dijon]" c="Dijon"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Le Castellet]" c="Le Castellet"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Magny Cours]" c="Magny Cours"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Reims]" c="Reims"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Rouen]" c="Rouen"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Hockenheim]" c="Hockenheim"/>
+        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Nürburg]" c="Nürburg"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Circuit].[Location Hierarchy].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="10" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+        <fieldUsage x="4"/>
+        <fieldUsage x="5"/>
+        <fieldUsage x="6"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition13.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481321874999" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1BD78FDA-7D69-4F13-9DC2-8B3D9C96FD22}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Degenerate Details].[Age Group].[Age Group]" caption="Age Group" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems count="5">
+        <s v="[Degenerate Details].[Age Group].&amp;[20-25]" c="20-25"/>
+        <s v="[Degenerate Details].[Age Group].&amp;[26-30]" c="26-30"/>
+        <s v="[Degenerate Details].[Age Group].&amp;[31-35]" c="31-35"/>
+        <s v="[Degenerate Details].[Age Group].&amp;[Over 35]" c="Over 35"/>
+        <s v="[Degenerate Details].[Age Group].&amp;[Under 20]" c="Under 20"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
+    <cacheField name="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" numFmtId="0" hierarchy="76" level="32767"/>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition14.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481324768516" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{125F41B5-3B3C-4D18-ADBF-159F41F79641}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
@@ -27658,8 +28397,889 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheDefinition15.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481327777779" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{EDAF3AB4-F84F-4D58-B645-530C9DA3FC38}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" numFmtId="0" hierarchy="78" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" numFmtId="0" hierarchy="79" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" numFmtId="0" hierarchy="80" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" numFmtId="0" hierarchy="81" level="32767"/>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="25">
+        <s v="[Dim Time].[Year].&amp;[2000]" c="2000"/>
+        <s v="[Dim Time].[Year].&amp;[2001]" c="2001"/>
+        <s v="[Dim Time].[Year].&amp;[2002]" c="2002"/>
+        <s v="[Dim Time].[Year].&amp;[2003]" c="2003"/>
+        <s v="[Dim Time].[Year].&amp;[2004]" c="2004"/>
+        <s v="[Dim Time].[Year].&amp;[2005]" c="2005"/>
+        <s v="[Dim Time].[Year].&amp;[2006]" c="2006"/>
+        <s v="[Dim Time].[Year].&amp;[2007]" c="2007"/>
+        <s v="[Dim Time].[Year].&amp;[2008]" c="2008"/>
+        <s v="[Dim Time].[Year].&amp;[2009]" c="2009"/>
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.482698958331" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{31C02256-19E7-4A55-B928-9C1309321BFA}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="9">
+    <cacheField name="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" numFmtId="0" hierarchy="78" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" numFmtId="0" hierarchy="79" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" numFmtId="0" hierarchy="80" level="32767"/>
+    <cacheField name="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" numFmtId="0" hierarchy="81" level="32767"/>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Year]" caption="Year" numFmtId="0" hierarchy="36" level="1">
+      <sharedItems count="25">
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2000]" c="2000"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2001]" c="2001"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2002]" c="2002"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2003]" c="2003"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2004]" c="2004"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2005]" c="2005"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2006]" c="2006"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2007]" c="2007"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2008]" c="2008"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2009]" c="2009"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="36" level="2">
+      <sharedItems count="4">
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2017].&amp;[1]" c="1"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2017].&amp;[2]" c="2"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2017].&amp;[3]" c="3"/>
+        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2017].&amp;[4]" c="4"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Month]" caption="Month" numFmtId="0" hierarchy="36" level="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Time Hierarchy].[Day Of Month]" caption="Day Of Month" numFmtId="0" hierarchy="36" level="4">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="5" unbalanced="0">
+      <fieldsUsage count="5">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+        <fieldUsage x="5"/>
+        <fieldUsage x="6"/>
+        <fieldUsage x="7"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="8"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" iconSet="10" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" iconSet="3" displayFolder="" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.565184375002" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1B23EE04-88D7-45FA-B735-CBAC80190CCC}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
+    <cacheField name="[Dim Status].[Status Hierarchy].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="27" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Status].[Status Hierarchy].[Status Category].&amp;[Accident/Incident]" c="Accident/Incident"/>
+        <s v="[Dim Status].[Status Hierarchy].[Status Category].&amp;[Driver Issue]" c="Driver Issue"/>
+        <s v="[Dim Status].[Status Hierarchy].[Status Category].&amp;[Mechanical Failure]" c="Mechanical Failure"/>
+        <s v="[Dim Status].[Status Hierarchy].[Status Category].&amp;[Pre-Race/Qualification]" c="Pre-Race/Qualification"/>
+        <s v="[Dim Status].[Status Hierarchy].[Status Category].&amp;[Race Outcome]" c="Race Outcome"/>
+        <s v="[Dim Status].[Status Hierarchy].[Status Category].&amp;[Sporting/Regulatory]" c="Sporting/Regulatory"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Status].[Status Hierarchy].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="27" level="2">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="3" unbalanced="0">
+      <fieldsUsage count="3">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" iconSet="10" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" iconSet="3" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.48128634259" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{8FE8892F-6B13-44C4-9323-FDA7B9542767}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="5">
+    <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
+      <sharedItems count="10">
+        <s v="[Dim Status].[Status Description].&amp;[Brakes]" c="Brakes"/>
+        <s v="[Dim Status].[Status Description].&amp;[Electrical]" c="Electrical"/>
+        <s v="[Dim Status].[Status Description].&amp;[Engine]" c="Engine"/>
+        <s v="[Dim Status].[Status Description].&amp;[Gearbox]" c="Gearbox"/>
+        <s v="[Dim Status].[Status Description].&amp;[Hydraulics]" c="Hydraulics"/>
+        <s v="[Dim Status].[Status Description].&amp;[Mechanical]" c="Mechanical"/>
+        <s v="[Dim Status].[Status Description].&amp;[Power Unit]" c="Power Unit"/>
+        <s v="[Dim Status].[Status Description].&amp;[Puncture]" c="Puncture"/>
+        <s v="[Dim Status].[Status Description].&amp;[Suspension]" c="Suspension"/>
+        <s v="[Dim Status].[Status Description].&amp;[Wheel]" c="Wheel"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Status].[Status Category].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="25" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Constructor].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650480902776" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{1BD78FDA-7D69-4F13-9DC2-8B3D9C96FD22}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481288888892" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{22B37FF6-6A8A-4281-AC48-8C27DD0DC8A1}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="6">
+    <cacheField name="[Dim Status].[Status Description].[Status Description]" caption="Status Description" numFmtId="0" hierarchy="26" level="1">
+      <sharedItems count="10">
+        <s v="[Dim Status].[Status Description].&amp;[Axle]" c="Axle"/>
+        <s v="[Dim Status].[Status Description].&amp;[Brakes]" c="Brakes"/>
+        <s v="[Dim Status].[Status Description].&amp;[Clutch]" c="Clutch"/>
+        <s v="[Dim Status].[Status Description].&amp;[Engine]" c="Engine"/>
+        <s v="[Dim Status].[Status Description].&amp;[Gearbox]" c="Gearbox"/>
+        <s v="[Dim Status].[Status Description].&amp;[Ignition]" c="Ignition"/>
+        <s v="[Dim Status].[Status Description].&amp;[Oil leak]" c="Oil leak"/>
+        <s v="[Dim Status].[Status Description].&amp;[Overheating]" c="Overheating"/>
+        <s v="[Dim Status].[Status Description].&amp;[Suspension]" c="Suspension"/>
+        <s v="[Dim Status].[Status Description].&amp;[Transmission]" c="Transmission"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Status].[Status Category].[Status Category]" caption="Status Category" numFmtId="0" hierarchy="25" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Measures].[Fact Result Count]" caption="Fact Result Count" numFmtId="0" hierarchy="53" level="32767"/>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Constructor].[Country Name].[Country Name]" caption="Country Name" numFmtId="0" hierarchy="13" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Constructor].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="12" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481293634257" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{91EA7F40-35C5-4637-AD47-C1EF62F40064}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Degenerate Details].[Age Group].[Age Group]" caption="Age Group" numFmtId="0" hierarchy="1" level="1">
@@ -27671,8 +29291,8 @@
         <s v="[Degenerate Details].[Age Group].&amp;[Under 20]" c="Under 20"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
-    <cacheField name="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" numFmtId="0" hierarchy="76" level="32767"/>
+    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
+    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
   </cacheFields>
   <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
@@ -27752,19 +29372,19 @@
     <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
@@ -27806,80 +29426,33 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650481944445" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{83FC3B7F-BBEF-4612-AC70-0D06FDFFB172}">
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481298148145" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5251863D-400F-43FD-A0F1-A4BBAAFEDC07}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="7">
-    <cacheField name="[Dim Circuit].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="7" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" numFmtId="0" hierarchy="69" level="32767"/>
-    <cacheField name="[Dim Circuit].[Circuit Name].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="6" level="1">
-      <sharedItems count="30">
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Charade Circuit]" c="Charade Circuit"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Nevers Magny-Cours]" c="Circuit de Nevers Magny-Cours"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Spa-Francorchamps]" c="Circuit de Spa-Francorchamps"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Paul Ricard]" c="Circuit Paul Ricard"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Dijon-Prenois]" c="Dijon-Prenois"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Hockenheimring]" c="Hockenheimring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Nivelles-Baulers]" c="Nivelles-Baulers"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Nürburgring]" c="Nürburgring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Red Bull Ring]" c="Red Bull Ring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Reims-Gueux]" c="Reims-Gueux"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Rouen-Les-Essarts]" c="Rouen-Les-Essarts"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Zolder]" c="Zolder"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Aintree]" u="1" c="Aintree"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Enzo e Dino Ferrari]" u="1" c="Autodromo Enzo e Dino Ferrari"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Autodromo Nazionale di Monza]" u="1" c="Autodromo Nazionale di Monza"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Autódromo do Estoril]" u="1" c="Autódromo do Estoril"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Brands Hatch]" u="1" c="Brands Hatch"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Bremgarten]" u="1" c="Circuit Bremgarten"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Barcelona-Catalunya]" u="1" c="Circuit de Barcelona-Catalunya"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Monaco]" u="1" c="Circuit de Monaco"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit de Pedralbes]" u="1" c="Circuit de Pedralbes"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuit Park Zandvoort]" u="1" c="Circuit Park Zandvoort"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Circuito de Jerez]" u="1" c="Circuito de Jerez"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Donington Park]" u="1" c="Donington Park"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Hungaroring]" u="1" c="Hungaroring"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Jarama]" u="1" c="Jarama"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Scandinavian Raceway]" u="1" c="Scandinavian Raceway"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Silverstone Circuit]" u="1" c="Silverstone Circuit"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Sochi Autodrom]" u="1" c="Sochi Autodrom"/>
-        <s v="[Dim Circuit].[Circuit Name].&amp;[Valencia Street Circuit]" u="1" c="Valencia Street Circuit"/>
+  <cacheFields count="5">
+    <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
+      <sharedItems count="2">
+        <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
+        <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Continent]" caption="Continent" numFmtId="0" hierarchy="10" level="1">
-      <sharedItems count="1">
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe]" c="Europe"/>
+    <cacheField name="[Dim Weather].[Track Temp Category].[Track Temp Category]" caption="Track Temp Category" numFmtId="0" hierarchy="42" level="1">
+      <sharedItems count="4">
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Cool Track]" c="Cool Track"/>
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Hot Track]" c="Hot Track"/>
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Optimal Track]" c="Optimal Track"/>
+        <s v="[Dim Weather].[Track Temp Category].&amp;[Very Hot Track]" c="Very Hot Track"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Country Name]" caption="Country Name" numFmtId="0" hierarchy="10" level="2">
-      <sharedItems count="4">
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria]" c="Austria"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium]" c="Belgium"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France]" c="France"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany]" c="Germany"/>
+    <cacheField name="[Dim Weather].[Wind Speed Category].[Wind Speed Category]" caption="Wind Speed Category" numFmtId="0" hierarchy="44" level="1">
+      <sharedItems count="3">
+        <s v="[Dim Weather].[Wind Speed Category].&amp;[Calm]" c="Calm"/>
+        <s v="[Dim Weather].[Wind Speed Category].&amp;[Light Breeze]" c="Light Breeze"/>
+        <s v="[Dim Weather].[Wind Speed Category].&amp;[Moderate Breeze]" c="Moderate Breeze"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Location City]" caption="Location City" numFmtId="0" hierarchy="10" level="3">
-      <sharedItems count="12">
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Austria].&amp;[Spielberg]" c="Spielberg"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Brussels]" c="Brussels"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Heusden-Zolder]" c="Heusden-Zolder"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Belgium].&amp;[Spa]" c="Spa"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Clermont-Ferrand]" c="Clermont-Ferrand"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Dijon]" c="Dijon"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Le Castellet]" c="Le Castellet"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Magny Cours]" c="Magny Cours"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Reims]" c="Reims"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[France].&amp;[Rouen]" c="Rouen"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Hockenheim]" c="Hockenheim"/>
-        <s v="[Dim Circuit].[Location Hierarchy].[Continent].&amp;[Europe].&amp;[Germany].&amp;[Nürburg]" c="Nürburg"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Circuit].[Location Hierarchy].[Circuit Name]" caption="Circuit Name" numFmtId="0" hierarchy="10" level="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
+    <cacheField name="[Measures].[DNF Percentage]" caption="DNF Percentage" numFmtId="0" hierarchy="75" level="32767"/>
+    <cacheField name="[Measures].[Finish Percentage]" caption="Finish Percentage" numFmtId="0" hierarchy="74" level="32767"/>
   </cacheFields>
   <cacheHierarchies count="82">
     <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
@@ -27888,29 +29461,11 @@
     <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="5" unbalanced="0">
-      <fieldsUsage count="5">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-        <fieldUsage x="4"/>
-        <fieldUsage x="5"/>
-        <fieldUsage x="6"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
@@ -27938,6 +29493,209 @@
     <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="4"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481301157408" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{3962C440-443E-4D75-B22B-0E43959F42B2}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="4">
+    <cacheField name="[Degenerate Details].[Grid Position].[Grid Position]" caption="Grid Position" numFmtId="0" hierarchy="4" level="1">
+      <sharedItems count="30">
+        <s v="[Degenerate Details].[Grid Position].&amp;[1]" c="1"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[2]" c="2"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[3]" c="3"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[4]" c="4"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[5]" c="5"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[6]" c="6"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[7]" c="7"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[8]" c="8"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[9]" c="9"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[10]" c="10"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[11]" c="11"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[12]" c="12"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[13]" c="13"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[14]" c="14"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[15]" c="15"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[16]" c="16"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[17]" c="17"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[18]" c="18"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[19]" c="19"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[20]" c="20"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[21]" c="21"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[22]" c="22"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[23]" c="23"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[24]" c="24"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[25]" c="25"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[26]" c="26"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[28]" u="1" c="28"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[29]" u="1" c="29"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[31]" u="1" c="31"/>
+        <s v="[Degenerate Details].[Grid Position].&amp;[32]" u="1" c="32"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Average Finish Position]" caption="Average Finish Position" numFmtId="0" hierarchy="72" level="32767"/>
+    <cacheField name="[Dim Race].[Race Name Official].[Race Name Official]" caption="Race Name Official" numFmtId="0" hierarchy="22" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
@@ -27969,12 +29727,180 @@
     <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
+  </cacheHierarchies>
+  <kpis count="1">
+    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
+  </kpis>
+  <dimensions count="9">
+    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
+    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
+    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
+    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
+    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
+    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
+    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
+    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Fact Result" caption="Fact Result"/>
+  </measureGroups>
+  <maps count="8">
+    <map measureGroup="0" dimension="0"/>
+    <map measureGroup="0" dimension="1"/>
+    <map measureGroup="0" dimension="2"/>
+    <map measureGroup="0" dimension="3"/>
+    <map measureGroup="0" dimension="4"/>
+    <map measureGroup="0" dimension="5"/>
+    <map measureGroup="0" dimension="6"/>
+    <map measureGroup="0" dimension="7"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481304050925" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{28154DEC-1536-40EA-A99D-9B5AD219ACD3}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
+    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems count="6">
+        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
+        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
+        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
+        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
+        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
+        <s v="[Dim Constructor].[Name].&amp;[Brawn]" u="1" c="Brawn"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
+      <sharedItems count="15">
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="82">
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
@@ -28022,39 +29948,56 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650482870369" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{19EFFABB-3DF1-4D82-9260-5ADF45140058}">
+<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481306944443" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C10063E3-D4E7-473D-BD5C-4113D4AFFA08}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="7">
-    <cacheField name="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" numFmtId="0" hierarchy="68" level="32767"/>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Year]" caption="Year" numFmtId="0" hierarchy="36" level="1">
-      <sharedItems count="6">
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Time Hierarchy].[Year].&amp;[2023]" c="2023"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Quarter]" caption="Quarter" numFmtId="0" hierarchy="36" level="2">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Month]" caption="Month" numFmtId="0" hierarchy="36" level="3">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Time].[Time Hierarchy].[Day Of Month]" caption="Day Of Month" numFmtId="0" hierarchy="36" level="4">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Dim Weather].[Did Rain Occur].[Did Rain Occur]" caption="Did Rain Occur" numFmtId="0" hierarchy="39" level="1">
-      <sharedItems count="3">
-        <s v="[Dim Weather].[Did Rain Occur].&amp;[No Rain]" c="No Rain"/>
-        <s v="[Dim Weather].[Did Rain Occur].&amp;[Rain Occurred]" c="Rain Occurred"/>
-        <s v="[Dim Weather].[Did Rain Occur].[All].UNKNOWNMEMBER" u="1" c="Unknown"/>
+  <cacheFields count="3">
+    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
+    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
+      <sharedItems count="23">
+        <s v="[Dim Constructor].[Name].&amp;[Alfa Romeo]" c="Alfa Romeo"/>
+        <s v="[Dim Constructor].[Name].&amp;[AlphaTauri]" c="AlphaTauri"/>
+        <s v="[Dim Constructor].[Name].&amp;[Alpine F1 Team]" c="Alpine F1 Team"/>
+        <s v="[Dim Constructor].[Name].&amp;[Aston Martin]" c="Aston Martin"/>
+        <s v="[Dim Constructor].[Name].&amp;[Caterham]" c="Caterham"/>
+        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
+        <s v="[Dim Constructor].[Name].&amp;[Force India]" c="Force India"/>
+        <s v="[Dim Constructor].[Name].&amp;[Haas F1 Team]" c="Haas F1 Team"/>
+        <s v="[Dim Constructor].[Name].&amp;[HRT]" c="HRT"/>
+        <s v="[Dim Constructor].[Name].&amp;[Lotus]" c="Lotus"/>
+        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
+        <s v="[Dim Constructor].[Name].&amp;[Manor Marussia]" c="Manor Marussia"/>
+        <s v="[Dim Constructor].[Name].&amp;[Marussia]" c="Marussia"/>
+        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
+        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
+        <s v="[Dim Constructor].[Name].&amp;[Racing Point]" c="Racing Point"/>
+        <s v="[Dim Constructor].[Name].&amp;[RB F1 Team]" c="RB F1 Team"/>
+        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
+        <s v="[Dim Constructor].[Name].&amp;[Renault]" c="Renault"/>
+        <s v="[Dim Constructor].[Name].&amp;[Sauber]" c="Sauber"/>
+        <s v="[Dim Constructor].[Name].&amp;[Toro Rosso]" c="Toro Rosso"/>
+        <s v="[Dim Constructor].[Name].&amp;[Virgin]" c="Virgin"/>
+        <s v="[Dim Constructor].[Name].&amp;[Williams]" c="Williams"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
+      <sharedItems count="15">
+        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
+        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
+        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
+        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
+        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
+        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
+        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
+        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
+        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
+        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
+        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
+        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
+        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
+        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
+        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <cacheHierarchies count="82">
@@ -28073,7 +30016,12 @@
     <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
@@ -28094,28 +30042,15 @@
     <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="5" unbalanced="0">
-      <fieldsUsage count="5">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-        <fieldUsage x="2"/>
-        <fieldUsage x="3"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
-        <fieldUsage x="6"/>
+        <fieldUsage x="2"/>
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="5"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
@@ -28144,13 +30079,13 @@
     <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0" oneField="1">
+    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
+    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
       <fieldsUsage count="1">
         <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
     <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
@@ -28198,194 +30133,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650483680554" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{70BBC5B2-939A-459F-88F4-8193C9E44ED3}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="6">
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Driver].[Full Name].[Full Name]" caption="Full Name" numFmtId="0" hierarchy="19" level="1">
-      <sharedItems count="9">
-        <s v="[Dim Driver].[Full Name].&amp;[Carlos Sainz]" c="Carlos Sainz"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Charles Leclerc]" c="Charles Leclerc"/>
-        <s v="[Dim Driver].[Full Name].&amp;[George Russell]" c="George Russell"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Kimi Räikkönen]" c="Kimi Räikkönen"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Lando Norris]" c="Lando Norris"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Lewis Hamilton]" c="Lewis Hamilton"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Max Verstappen]" c="Max Verstappen"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Sebastian Vettel]" c="Sebastian Vettel"/>
-        <s v="[Dim Driver].[Full Name].&amp;[Valtteri Bottas]" c="Valtteri Bottas"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Driver].[Continent].[Continent]" caption="Continent" numFmtId="0" hierarchy="16" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0"/>
-    </cacheField>
-    <cacheField name="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" numFmtId="0" hierarchy="73" level="32767"/>
-    <cacheField name="[Dim Race].[Year Season].[Year Season]" caption="Year Season" numFmtId="0" hierarchy="24" level="1">
-      <sharedItems count="7">
-        <s v="[Dim Race].[Year Season].&amp;[2018]" c="2018"/>
-        <s v="[Dim Race].[Year Season].&amp;[2019]" c="2019"/>
-        <s v="[Dim Race].[Year Season].&amp;[2020]" c="2020"/>
-        <s v="[Dim Race].[Year Season].&amp;[2021]" c="2021"/>
-        <s v="[Dim Race].[Year Season].&amp;[2022]" c="2022"/>
-        <s v="[Dim Race].[Year Season].&amp;[2023]" c="2023"/>
-        <s v="[Dim Race].[Year Season].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="4"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650484606478" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{6819B2E0-02BE-4505-B7D4-5934BA61994A}">
+<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45810.481310069445" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{6819B2E0-02BE-4505-B7D4-5934BA61994A}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="4">
     <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
@@ -28571,361 +30320,8 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.650485416663" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{C10063E3-D4E7-473D-BD5C-4113D4AFFA08}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
-    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems count="23">
-        <s v="[Dim Constructor].[Name].&amp;[Alfa Romeo]" c="Alfa Romeo"/>
-        <s v="[Dim Constructor].[Name].&amp;[AlphaTauri]" c="AlphaTauri"/>
-        <s v="[Dim Constructor].[Name].&amp;[Alpine F1 Team]" c="Alpine F1 Team"/>
-        <s v="[Dim Constructor].[Name].&amp;[Aston Martin]" c="Aston Martin"/>
-        <s v="[Dim Constructor].[Name].&amp;[Caterham]" c="Caterham"/>
-        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
-        <s v="[Dim Constructor].[Name].&amp;[Force India]" c="Force India"/>
-        <s v="[Dim Constructor].[Name].&amp;[Haas F1 Team]" c="Haas F1 Team"/>
-        <s v="[Dim Constructor].[Name].&amp;[HRT]" c="HRT"/>
-        <s v="[Dim Constructor].[Name].&amp;[Lotus]" c="Lotus"/>
-        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
-        <s v="[Dim Constructor].[Name].&amp;[Manor Marussia]" c="Manor Marussia"/>
-        <s v="[Dim Constructor].[Name].&amp;[Marussia]" c="Marussia"/>
-        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
-        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
-        <s v="[Dim Constructor].[Name].&amp;[Racing Point]" c="Racing Point"/>
-        <s v="[Dim Constructor].[Name].&amp;[RB F1 Team]" c="RB F1 Team"/>
-        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
-        <s v="[Dim Constructor].[Name].&amp;[Renault]" c="Renault"/>
-        <s v="[Dim Constructor].[Name].&amp;[Sauber]" c="Sauber"/>
-        <s v="[Dim Constructor].[Name].&amp;[Toro Rosso]" c="Toro Rosso"/>
-        <s v="[Dim Constructor].[Name].&amp;[Virgin]" c="Virgin"/>
-        <s v="[Dim Constructor].[Name].&amp;[Williams]" c="Williams"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="15">
-        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
-        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
-        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
-        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
-        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
-        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
-        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
-        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="Jantar" refreshedDate="45809.65048611111" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{28154DEC-1536-40EA-A99D-9B5AD219ACD3}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="3">
-    <cacheField name="[Measures].[Average Points]" caption="Average Points" numFmtId="0" hierarchy="70" level="32767"/>
-    <cacheField name="[Dim Constructor].[Name].[Name]" caption="Name" numFmtId="0" hierarchy="15" level="1">
-      <sharedItems count="6">
-        <s v="[Dim Constructor].[Name].&amp;[Ferrari]" c="Ferrari"/>
-        <s v="[Dim Constructor].[Name].&amp;[Lotus F1]" c="Lotus F1"/>
-        <s v="[Dim Constructor].[Name].&amp;[McLaren]" c="McLaren"/>
-        <s v="[Dim Constructor].[Name].&amp;[Mercedes]" c="Mercedes"/>
-        <s v="[Dim Constructor].[Name].&amp;[Red Bull]" c="Red Bull"/>
-        <s v="[Dim Constructor].[Name].&amp;[Brawn]" u="1" c="Brawn"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Dim Time].[Year].[Year]" caption="Year" numFmtId="0" hierarchy="37" level="1">
-      <sharedItems count="15">
-        <s v="[Dim Time].[Year].&amp;[2010]" c="2010"/>
-        <s v="[Dim Time].[Year].&amp;[2011]" c="2011"/>
-        <s v="[Dim Time].[Year].&amp;[2012]" c="2012"/>
-        <s v="[Dim Time].[Year].&amp;[2013]" c="2013"/>
-        <s v="[Dim Time].[Year].&amp;[2014]" c="2014"/>
-        <s v="[Dim Time].[Year].&amp;[2015]" c="2015"/>
-        <s v="[Dim Time].[Year].&amp;[2016]" c="2016"/>
-        <s v="[Dim Time].[Year].&amp;[2017]" c="2017"/>
-        <s v="[Dim Time].[Year].&amp;[2018]" c="2018"/>
-        <s v="[Dim Time].[Year].&amp;[2019]" c="2019"/>
-        <s v="[Dim Time].[Year].&amp;[2020]" c="2020"/>
-        <s v="[Dim Time].[Year].&amp;[2021]" c="2021"/>
-        <s v="[Dim Time].[Year].&amp;[2022]" c="2022"/>
-        <s v="[Dim Time].[Year].&amp;[2023]" c="2023"/>
-        <s v="[Dim Time].[Year].&amp;[2024]" c="2024"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="82">
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age At Race]" caption="Age At Race" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age At Race].[All]" allUniqueName="[Degenerate Details].[Age At Race].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Age Group]" caption="Age Group" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Age Group].[All]" allUniqueName="[Degenerate Details].[Age Group].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Composite Key]" caption="Composite Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Degenerate Details].[Composite Key].[All]" allUniqueName="[Degenerate Details].[Composite Key].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Final Position Order]" caption="Final Position Order" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Final Position Order].[All]" allUniqueName="[Degenerate Details].[Final Position Order].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Degenerate Details].[Grid Position]" caption="Grid Position" attribute="1" defaultMemberUniqueName="[Degenerate Details].[Grid Position].[All]" allUniqueName="[Degenerate Details].[Grid Position].[All]" dimensionUniqueName="[Degenerate Details]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Key]" caption="Circuit Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Key].[All]" allUniqueName="[Dim Circuit].[Circuit Key].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Circuit Name]" caption="Circuit Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Circuit Name].[All]" allUniqueName="[Dim Circuit].[Circuit Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Continent].[All]" allUniqueName="[Dim Circuit].[Continent].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Country Name].[All]" allUniqueName="[Dim Circuit].[Country Name].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location City]" caption="Location City" attribute="1" defaultMemberUniqueName="[Dim Circuit].[Location City].[All]" allUniqueName="[Dim Circuit].[Location City].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Circuit].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Circuit].[Location Hierarchy].[All]" allUniqueName="[Dim Circuit].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Circuit]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Constructor Key]" caption="Constructor Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Constructor].[Constructor Key].[All]" allUniqueName="[Dim Constructor].[Constructor Key].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Continent].[All]" allUniqueName="[Dim Constructor].[Continent].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Country Name].[All]" allUniqueName="[Dim Constructor].[Country Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Constructor].[Location Hierarchy].[All]" allUniqueName="[Dim Constructor].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Constructor].[Name]" caption="Name" attribute="1" defaultMemberUniqueName="[Dim Constructor].[Name].[All]" allUniqueName="[Dim Constructor].[Name].[All]" dimensionUniqueName="[Dim Constructor]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Driver].[Continent]" caption="Continent" attribute="1" defaultMemberUniqueName="[Dim Driver].[Continent].[All]" allUniqueName="[Dim Driver].[Continent].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Country Name]" caption="Country Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Country Name].[All]" allUniqueName="[Dim Driver].[Country Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Driver Key]" caption="Driver Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Driver].[Driver Key].[All]" allUniqueName="[Dim Driver].[Driver Key].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Full Name]" caption="Full Name" attribute="1" defaultMemberUniqueName="[Dim Driver].[Full Name].[All]" allUniqueName="[Dim Driver].[Full Name].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Driver].[Location Hierarchy]" caption="Location Hierarchy" defaultMemberUniqueName="[Dim Driver].[Location Hierarchy].[All]" allUniqueName="[Dim Driver].[Location Hierarchy].[All]" dimensionUniqueName="[Dim Driver]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Key]" caption="Race Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Race].[Race Key].[All]" allUniqueName="[Dim Race].[Race Key].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Race Name Official]" caption="Race Name Official" attribute="1" defaultMemberUniqueName="[Dim Race].[Race Name Official].[All]" allUniqueName="[Dim Race].[Race Name Official].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Round Number In Season]" caption="Round Number In Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Round Number In Season].[All]" allUniqueName="[Dim Race].[Round Number In Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Race].[Year Season]" caption="Year Season" attribute="1" defaultMemberUniqueName="[Dim Race].[Year Season].[All]" allUniqueName="[Dim Race].[Year Season].[All]" dimensionUniqueName="[Dim Race]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Category]" caption="Status Category" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Category].[All]" allUniqueName="[Dim Status].[Status Category].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Description]" caption="Status Description" attribute="1" defaultMemberUniqueName="[Dim Status].[Status Description].[All]" allUniqueName="[Dim Status].[Status Description].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Hierarchy]" caption="Status Hierarchy" defaultMemberUniqueName="[Dim Status].[Status Hierarchy].[All]" allUniqueName="[Dim Status].[Status Hierarchy].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Status].[Status Key]" caption="Status Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Status].[Status Key].[All]" allUniqueName="[Dim Status].[Status Key].[All]" dimensionUniqueName="[Dim Status]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Date Key]" caption="Date Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Time].[Date Key].[All]" allUniqueName="[Dim Time].[Date Key].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Month]" caption="Day Of Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Month].[All]" allUniqueName="[Dim Time].[Day Of Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Day Of Week Name]" caption="Day Of Week Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Day Of Week Name].[All]" allUniqueName="[Dim Time].[Day Of Week Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Full Date]" caption="Full Date" attribute="1" defaultMemberUniqueName="[Dim Time].[Full Date].[All]" allUniqueName="[Dim Time].[Full Date].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Dim Time].[Month].[All]" allUniqueName="[Dim Time].[Month].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Month Name]" caption="Month Name" attribute="1" defaultMemberUniqueName="[Dim Time].[Month Name].[All]" allUniqueName="[Dim Time].[Month Name].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Quarter]" caption="Quarter" attribute="1" defaultMemberUniqueName="[Dim Time].[Quarter].[All]" allUniqueName="[Dim Time].[Quarter].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Time Hierarchy]" caption="Time Hierarchy" defaultMemberUniqueName="[Dim Time].[Time Hierarchy].[All]" allUniqueName="[Dim Time].[Time Hierarchy].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Time].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Dim Time].[Year].[All]" allUniqueName="[Dim Time].[Year].[All]" dimensionUniqueName="[Dim Time]" displayFolder="" count="2" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Dim Weather].[Air Temp Category]" caption="Air Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Air Temp Category].[All]" allUniqueName="[Dim Weather].[Air Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Did Rain Occur]" caption="Did Rain Occur" attribute="1" defaultMemberUniqueName="[Dim Weather].[Did Rain Occur].[All]" allUniqueName="[Dim Weather].[Did Rain Occur].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Humidity Category]" caption="Humidity Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Humidity Category].[All]" allUniqueName="[Dim Weather].[Humidity Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Pressure Category]" caption="Pressure Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Pressure Category].[All]" allUniqueName="[Dim Weather].[Pressure Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Track Temp Category]" caption="Track Temp Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Track Temp Category].[All]" allUniqueName="[Dim Weather].[Track Temp Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Weather Key]" caption="Weather Key" attribute="1" keyAttribute="1" defaultMemberUniqueName="[Dim Weather].[Weather Key].[All]" allUniqueName="[Dim Weather].[Weather Key].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Dim Weather].[Wind Speed Category]" caption="Wind Speed Category" attribute="1" defaultMemberUniqueName="[Dim Weather].[Wind Speed Category].[All]" allUniqueName="[Dim Weather].[Wind Speed Category].[All]" dimensionUniqueName="[Dim Weather]" displayFolder="" count="0" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Points Scored]" caption="Points Scored" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Laps Completed]" caption="Laps Completed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops]" caption="Number Of Pit Stops" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds]" caption="Race Time Milliseconds" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Position Order Change]" caption="Position Order Change" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Rank Fastest Lap]" caption="Rank Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed]" caption="Fastest Lap Top Speed" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Age At Race]" caption="Age At Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fact Result Count]" caption="Fact Result Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Number Of Pit Stops Count]" caption="Number Of Pit Stops Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Win]" caption="Is Win" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finished Race]" caption="Finished Race" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Podium]" caption="Is Podium" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is DNF]" caption="Is DNF" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Pole Position]" caption="Is Pole Position" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Is Fastest Lap]" caption="Is Fastest Lap" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Outside Top10 Grid]" caption="Podium From Outside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Podium From Inside Top10 Grid]" caption="Podium From Inside Top10 Grid" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Final Position Order]" caption="Final Position Order" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Fastest Lap Top Speed Count]" caption="Fastest Lap Top Speed Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Milliseconds Count]" caption="Race Time Milliseconds Count" measure="1" displayFolder="" measureGroup="Fact Result" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Race Time Formatted]" caption="Race Time Formatted" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Absolute Position Order Change]" caption="Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[AveragePitStopsCount]" caption="AveragePitStopsCount" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Absolute Position Order Change]" caption="Average Absolute Position Order Change" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Points]" caption="Average Points" measure="1" displayFolder="" count="0" oneField="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Number of Wins]" caption="Number of Wins" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Finish Position]" caption="Average Finish Position" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Win Percentage from Grid]" caption="Win Percentage from Grid" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Finish Percentage]" caption="Finish Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[DNF Percentage]" caption="DNF Percentage" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Fastest Lap Top Speed]" caption="Average Fastest Lap Top Speed" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Average Race Time in Minutes]" caption="Average Race Time in Minutes" measure="1" displayFolder="" count="0"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Value]" caption="Constructor Reliability KPI" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Goal]" caption="Constructor Reliability KPI (Goal)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Status]" caption="Constructor Reliability KPI (Status)" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Constructor Reliability KPI Trend]" caption="Constructor Reliability KPI (Trend)" measure="1" displayFolder="" count="0" hidden="1"/>
-  </cacheHierarchies>
-  <kpis count="1">
-    <kpi uniqueName="Constructor Reliability KPI" caption="Constructor Reliability KPI" displayFolder="" parent="" value="[Measures].[Constructor Reliability KPI Value]" goal="[Measures].[Constructor Reliability KPI Goal]" status="[Measures].[Constructor Reliability KPI Status]" trend="[Measures].[Constructor Reliability KPI Trend]" weight=""/>
-  </kpis>
-  <dimensions count="9">
-    <dimension name="Degenerate Details" uniqueName="[Degenerate Details]" caption="Degenerate Details"/>
-    <dimension name="Dim Circuit" uniqueName="[Dim Circuit]" caption="Dim Circuit"/>
-    <dimension name="Dim Constructor" uniqueName="[Dim Constructor]" caption="Dim Constructor"/>
-    <dimension name="Dim Driver" uniqueName="[Dim Driver]" caption="Dim Driver"/>
-    <dimension name="Dim Race" uniqueName="[Dim Race]" caption="Dim Race"/>
-    <dimension name="Dim Status" uniqueName="[Dim Status]" caption="Dim Status"/>
-    <dimension name="Dim Time" uniqueName="[Dim Time]" caption="Dim Time"/>
-    <dimension name="Dim Weather" uniqueName="[Dim Weather]" caption="Dim Weather"/>
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Fact Result" caption="Fact Result"/>
-  </measureGroups>
-  <maps count="8">
-    <map measureGroup="0" dimension="0"/>
-    <map measureGroup="0" dimension="1"/>
-    <map measureGroup="0" dimension="2"/>
-    <map measureGroup="0" dimension="3"/>
-    <map measureGroup="0" dimension="4"/>
-    <map measureGroup="0" dimension="5"/>
-    <map measureGroup="0" dimension="6"/>
-    <map measureGroup="0" dimension="7"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{56F7BB47-9FE9-44F6-BAE3-68381FD572F9}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:D12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -29187,7 +30583,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{64550925-18BC-4527-BBCE-E54A3262D0D6}" name="PivotTable1" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A1:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29364,7 +30760,350 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="10">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="11">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
+    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
+    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="11">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="8"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="9"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="7"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="1" level="1">
+        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="11" level="1">
+        <member name="[Dim Time].[Year].&amp;[2010]"/>
+        <member name="[Dim Time].[Year].&amp;[2011]"/>
+        <member name="[Dim Time].[Year].&amp;[2012]"/>
+        <member name="[Dim Time].[Year].&amp;[2013]"/>
+        <member name="[Dim Time].[Year].&amp;[2014]"/>
+        <member name="[Dim Time].[Year].&amp;[2015]"/>
+        <member name="[Dim Time].[Year].&amp;[2016]"/>
+        <member name="[Dim Time].[Year].&amp;[2017]"/>
+        <member name="[Dim Time].[Year].&amp;[2018]"/>
+        <member name="[Dim Time].[Year].&amp;[2019]"/>
+        <member name="[Dim Time].[Year].&amp;[2020]"/>
+      </members>
+    </pivotHierarchy>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <filters count="1">
+    <filter fld="0" type="count" id="1" iMeasureHier="53">
+      <autoFilter ref="A1">
+        <filterColumn colId="0">
+          <top10 val="10" filterVal="10"/>
+        </filterColumn>
+      </autoFilter>
+    </filter>
+  </filters>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="26"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A746FFF8-6B66-4252-8CEA-043143963F3D}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
   <pivotFields count="6">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -29711,351 +31450,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable12.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5AA7137E-FDF2-411F-A7E9-D7AEEDDD54ED}" name="PivotTable4" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
-  <location ref="F5:G16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
-  <pivotFields count="5">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" measureFilter="1" sortType="descending" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="10">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="11">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <pageFields count="3">
-    <pageField fld="1" hier="25" name="[Dim Status].[Status Category].&amp;[Mechanical Failure]" cap="Mechanical Failure"/>
-    <pageField fld="3" hier="37" name="[Dim Time].[Year].&amp;[2010]" cap="2010"/>
-    <pageField fld="4" hier="12" name="[Dim Constructor].[Continent].&amp;[Europe]" cap="Europe"/>
-  </pageFields>
-  <dataFields count="1">
-    <dataField fld="2" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="11">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="4">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="8"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="6"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="4"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="7">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="9"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="8">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="7"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="0" count="1" selected="0">
-            <x v="5"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="83">
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Constructor].[Continent].&amp;[Europe]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="1" level="1">
-        <member name="[Dim Status].[Status Category].&amp;[Mechanical Failure]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy multipleItemSelectionAllowed="1">
-      <members count="11" level="1">
-        <member name="[Dim Time].[Year].&amp;[2010]"/>
-        <member name="[Dim Time].[Year].&amp;[2011]"/>
-        <member name="[Dim Time].[Year].&amp;[2012]"/>
-        <member name="[Dim Time].[Year].&amp;[2013]"/>
-        <member name="[Dim Time].[Year].&amp;[2014]"/>
-        <member name="[Dim Time].[Year].&amp;[2015]"/>
-        <member name="[Dim Time].[Year].&amp;[2016]"/>
-        <member name="[Dim Time].[Year].&amp;[2017]"/>
-        <member name="[Dim Time].[Year].&amp;[2018]"/>
-        <member name="[Dim Time].[Year].&amp;[2019]"/>
-        <member name="[Dim Time].[Year].&amp;[2020]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <filters count="1">
-    <filter fld="0" type="count" id="1" iMeasureHier="53">
-      <autoFilter ref="A1">
-        <filterColumn colId="0">
-          <top10 val="10" filterVal="10"/>
-        </filterColumn>
-      </autoFilter>
-    </filter>
-  </filters>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="26"/>
-  </rowHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable13.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8EE1C926-7098-4912-8FCE-3C5B6C4A9ADA}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" fieldListSortAscending="1">
   <location ref="A1:G7" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -30310,7 +31706,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable14.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8B5532C8-184E-45A3-9671-D5D71185BFA5}" name="PivotTable6" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A3:B78" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -30749,7 +32145,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable15.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB381D15-99CD-4BB2-BFAA-5B743EDB0261}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB381D15-99CD-4BB2-BFAA-5B743EDB0261}" name="PivotTable1" cacheId="14" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
   <location ref="A3:E29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -30893,6 +32289,304 @@
     <dataField name="Constructor Reliability KPI Trend" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="2">
+    <conditionalFormat scope="data" priority="2">
+      <pivotAreas count="1">
+        <pivotArea outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="2"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+    <conditionalFormat scope="data" priority="1">
+      <pivotAreas count="1">
+        <pivotArea outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="3"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </pivotAreas>
+    </conditionalFormat>
+  </conditionalFormats>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="37"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable16.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7064D5D5-6773-4CD8-9F32-6679555721C2}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" fieldListSortAscending="1">
+  <location ref="A3:E33" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="9">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="25">
+        <item c="1" x="0"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+        <item c="1" x="3"/>
+        <item c="1" x="4"/>
+        <item c="1" x="5"/>
+        <item c="1" x="6"/>
+        <item c="1" x="7"/>
+        <item c="1" x="8"/>
+        <item c="1" x="9"/>
+        <item c="1" x="10"/>
+        <item c="1" x="11"/>
+        <item c="1" x="12"/>
+        <item c="1" x="13"/>
+        <item c="1" x="14"/>
+        <item c="1" x="15"/>
+        <item c="1" x="16"/>
+        <item c="1" x="17" d="1"/>
+        <item c="1" x="18"/>
+        <item c="1" x="19"/>
+        <item c="1" x="20"/>
+        <item c="1" x="21"/>
+        <item c="1" x="22"/>
+        <item c="1" x="23"/>
+        <item c="1" x="24"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="4">
+        <item c="1" x="0"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+        <item c="1" x="3"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
+    <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="4"/>
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="30">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i r="1">
+      <x/>
+    </i>
+    <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+    <i i="3">
+      <x v="3"/>
+    </i>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="8" hier="37" name="[Dim Time].[Year].&amp;[2000]" cap="2000"/>
+  </pageFields>
+  <dataFields count="4">
+    <dataField name="Constructor Reliability KPI" fld="0" baseField="0" baseItem="0"/>
+    <dataField name="Constructor Reliability KPI Goal" fld="1" baseField="0" baseItem="0"/>
+    <dataField name="Constructor Reliability KPI Status" fld="2" baseField="0" baseItem="0"/>
+    <dataField name="Constructor Reliability KPI Trend" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <conditionalFormats count="2">
     <conditionalFormat scope="data" priority="1">
       <pivotAreas count="1">
         <pivotArea outline="0" fieldPosition="0">
@@ -30954,7 +32648,35 @@
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
-    <pivotHierarchy/>
+    <pivotHierarchy multipleItemSelectionAllowed="1">
+      <members count="25" level="1">
+        <member name="[Dim Time].[Year].&amp;[2000]"/>
+        <member name="[Dim Time].[Year].&amp;[2001]"/>
+        <member name="[Dim Time].[Year].&amp;[2002]"/>
+        <member name="[Dim Time].[Year].&amp;[2003]"/>
+        <member name="[Dim Time].[Year].&amp;[2004]"/>
+        <member name="[Dim Time].[Year].&amp;[2005]"/>
+        <member name="[Dim Time].[Year].&amp;[2006]"/>
+        <member name="[Dim Time].[Year].&amp;[2007]"/>
+        <member name="[Dim Time].[Year].&amp;[2008]"/>
+        <member name="[Dim Time].[Year].&amp;[2009]"/>
+        <member name="[Dim Time].[Year].&amp;[2010]"/>
+        <member name="[Dim Time].[Year].&amp;[2011]"/>
+        <member name="[Dim Time].[Year].&amp;[2012]"/>
+        <member name="[Dim Time].[Year].&amp;[2013]"/>
+        <member name="[Dim Time].[Year].&amp;[2014]"/>
+        <member name="[Dim Time].[Year].&amp;[2015]"/>
+        <member name="[Dim Time].[Year].&amp;[2016]"/>
+        <member name="[Dim Time].[Year].&amp;[2017]"/>
+        <member name="[Dim Time].[Year].&amp;[2018]"/>
+        <member name="[Dim Time].[Year].&amp;[2019]"/>
+        <member name="[Dim Time].[Year].&amp;[2020]"/>
+        <member name="[Dim Time].[Year].&amp;[2021]"/>
+        <member name="[Dim Time].[Year].&amp;[2022]"/>
+        <member name="[Dim Time].[Year].&amp;[2023]"/>
+        <member name="[Dim Time].[Year].&amp;[2024]"/>
+      </members>
+    </pivotHierarchy>
     <pivotHierarchy/>
     <pivotHierarchy/>
     <pivotHierarchy/>
@@ -31003,7 +32725,7 @@
   </pivotHierarchies>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="37"/>
+    <rowHierarchyUsage hierarchyUsage="36"/>
   </rowHierarchiesUsage>
   <colHierarchiesUsage count="1">
     <colHierarchyUsage hierarchyUsage="-2"/>
@@ -31019,8 +32741,168 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable17.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{30CF1DCF-C01A-4FF1-813C-1DB01E89E0AE}" name="PivotTable1" cacheId="86" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+  <location ref="A1:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0">
+      <items count="6">
+        <item c="1" x="0"/>
+        <item c="1" x="1"/>
+        <item c="1" x="2"/>
+        <item c="1" x="3"/>
+        <item c="1" x="4"/>
+        <item c="1" x="5"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField fld="0" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotHierarchies count="83">
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragOff="0"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="27"/>
+  </rowHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C46A81BC-8C75-4F76-8210-EEF5A83AF696}" name="PivotTable4" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10" fieldListSortAscending="1">
   <location ref="A4:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="7">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
@@ -31837,7 +33719,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0D28268D-F139-414C-88E2-408A6595ABF9}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="15" fieldListSortAscending="1">
   <location ref="A3:G5" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="3">
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -32096,7 +33978,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F77C5366-9A19-47B5-8C19-F54DD5D444B7}" name="PivotTable4" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="11" fieldListSortAscending="1">
   <location ref="K5:U14" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="5">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32453,7 +34335,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2F74144B-8497-4A58-998A-35E2F835E367}" name="PivotTable1" cacheId="8" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5" fieldListSortAscending="1">
   <location ref="A4:B31" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisPage" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -32719,7 +34601,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FA00D414-BC42-451C-9F10-3DB99A7CAD38}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" fieldListSortAscending="1">
   <location ref="A5:B32" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="2" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -33032,7 +34914,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F4BABA1E-A83D-4CB8-B63A-6BD641FCE2BF}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A1:C29" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -33291,7 +35173,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7F60A7DA-9FE7-47E8-A86B-C8A0C2243D7A}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2" fieldListSortAscending="1">
   <location ref="A12:C18" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -35075,6 +36957,651 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27E065A7-A0E8-4448-9050-48709B63BD6A}">
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s" vm="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B4" s="5">
+        <v>0.58981233243967823</v>
+      </c>
+      <c r="C4">
+        <v>0.8</v>
+      </c>
+      <c r="D4">
+        <v>-1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.5802139037433155</v>
+      </c>
+      <c r="C5">
+        <v>0.8</v>
+      </c>
+      <c r="D5">
+        <v>-1</v>
+      </c>
+      <c r="E5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.55524861878453047</v>
+      </c>
+      <c r="C6">
+        <v>0.8</v>
+      </c>
+      <c r="D6">
+        <v>-1</v>
+      </c>
+      <c r="E6">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.65312499999999996</v>
+      </c>
+      <c r="C7">
+        <v>0.8</v>
+      </c>
+      <c r="D7">
+        <v>-1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.71944444444444444</v>
+      </c>
+      <c r="C8">
+        <v>0.8</v>
+      </c>
+      <c r="D8">
+        <v>-1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.7393617021276595</v>
+      </c>
+      <c r="C9">
+        <v>0.8</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.67929292929292928</v>
+      </c>
+      <c r="C10">
+        <v>0.8</v>
+      </c>
+      <c r="D10">
+        <v>-1</v>
+      </c>
+      <c r="E10">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.73262032085561501</v>
+      </c>
+      <c r="C11">
+        <v>0.8</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.76358695652173914</v>
+      </c>
+      <c r="C12">
+        <v>0.8</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.80294117647058827</v>
+      </c>
+      <c r="C13">
+        <v>0.8</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.74780701754385959</v>
+      </c>
+      <c r="C14">
+        <v>0.8</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B15" s="5">
+        <v>0.83114035087719296</v>
+      </c>
+      <c r="C15">
+        <v>0.8</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B16" s="5">
+        <v>0.82291666666666663</v>
+      </c>
+      <c r="C16">
+        <v>0.8</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="5">
+        <v>0.85406698564593297</v>
+      </c>
+      <c r="C17">
+        <v>0.8</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.80835380835380832</v>
+      </c>
+      <c r="C18">
+        <v>0.8</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.81746031746031744</v>
+      </c>
+      <c r="C19">
+        <v>0.8</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B20" s="5">
+        <v>0.83982683982683981</v>
+      </c>
+      <c r="C20">
+        <v>0.8</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="C22">
+        <v>0.8</v>
+      </c>
+      <c r="D22">
+        <v>-1</v>
+      </c>
+      <c r="E22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.72142857142857142</v>
+      </c>
+      <c r="C23">
+        <v>0.8</v>
+      </c>
+      <c r="D23">
+        <v>0</v>
+      </c>
+      <c r="E23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="5">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="C24">
+        <v>0.8</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0.81666666666666665</v>
+      </c>
+      <c r="C25">
+        <v>0.8</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0.80238095238095242</v>
+      </c>
+      <c r="C26">
+        <v>0.8</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.86190476190476195</v>
+      </c>
+      <c r="C27">
+        <v>0.8</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.83529411764705885</v>
+      </c>
+      <c r="C28">
+        <v>0.8</v>
+      </c>
+      <c r="D28">
+        <v>1</v>
+      </c>
+      <c r="E28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0.8727272727272728</v>
+      </c>
+      <c r="C29">
+        <v>0.8</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="5">
+        <v>0.83181818181818179</v>
+      </c>
+      <c r="C30">
+        <v>0.8</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
+      </c>
+      <c r="E30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="5">
+        <v>0.85681818181818181</v>
+      </c>
+      <c r="C31">
+        <v>0.8</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5">
+        <v>0.90605427974947805</v>
+      </c>
+      <c r="C32">
+        <v>0.8</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="5">
+        <v>0.77666435162218472</v>
+      </c>
+      <c r="C33">
+        <v>0.8</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting pivot="1" sqref="D4:D33">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Signs" showValue="0">
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="-0.5"/>
+        <cfvo type="num" val="0.5"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting pivot="1" sqref="E4:E33">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="5Arrows" showValue="0">
+        <cfvo type="num" val="-1"/>
+        <cfvo type="num" val="-0.5"/>
+        <cfvo type="num" val="-0.01"/>
+        <cfvo type="num" val="0.01"/>
+        <cfvo type="num" val="0.5"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B87FD18-0A42-43CC-AC63-C9109E20031B}">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="8">
+        <v>2781</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="8">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4" s="8">
+        <v>6696</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B5" s="8">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B6" s="8">
+        <v>15441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B7" s="8">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="8">
+        <v>26756</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{253A2E13-AB7A-4EED-ADB2-AA4F27F23C82}">
   <dimension ref="A2:B22"/>
@@ -35267,8 +37794,9 @@
   <cols>
     <col min="1" max="1" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="12" width="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="7.42578125" bestFit="1" customWidth="1"/>
@@ -36760,8 +39288,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -37208,22 +39736,22 @@
       <c r="A4" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4">
         <v>3</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4">
         <v>132</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4">
         <v>6</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4">
         <v>39</v>
       </c>
-      <c r="F4" s="8">
+      <c r="F4">
         <v>9</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4">
         <v>171</v>
       </c>
     </row>
@@ -37231,22 +39759,22 @@
       <c r="A5" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5">
         <v>5</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5">
         <v>121</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5">
         <v>2</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5">
         <v>46</v>
       </c>
-      <c r="F5" s="8">
+      <c r="F5">
         <v>7</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5">
         <v>167</v>
       </c>
     </row>
@@ -37254,18 +39782,16 @@
       <c r="A6" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6">
         <v>1</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6">
         <v>5</v>
       </c>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8">
+      <c r="F6">
         <v>1</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
@@ -37273,22 +39799,22 @@
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7">
         <v>9</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7">
         <v>258</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7">
         <v>8</v>
       </c>
-      <c r="E7" s="8">
+      <c r="E7">
         <v>85</v>
       </c>
-      <c r="F7" s="8">
+      <c r="F7">
         <v>17</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7">
         <v>343</v>
       </c>
     </row>
